--- a/submissions/excel/excel_09_workbook_redesign.xlsx
+++ b/submissions/excel/excel_09_workbook_redesign.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\venti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9480AD-CE7B-414A-A363-EDCD152D2709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28D0AF6-BCC9-4753-AC1D-5F90AD48DFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actuals" sheetId="14" r:id="rId1"/>
@@ -19,15 +19,14 @@
     <sheet name="Jan 2026 A vs F " sheetId="9" r:id="rId4"/>
     <sheet name="Feb 2026 A vs F" sheetId="12" r:id="rId5"/>
     <sheet name="Mar 2026 A vs F" sheetId="13" r:id="rId6"/>
-    <sheet name="Apr 2026 A vs F" sheetId="15" r:id="rId7"/>
-    <sheet name="2026 Forecast" sheetId="3" r:id="rId8"/>
-    <sheet name="KPI Tracker" sheetId="10" r:id="rId9"/>
-    <sheet name="Waterfall Data" sheetId="11" r:id="rId10"/>
-    <sheet name="Engine" sheetId="8" r:id="rId11"/>
-    <sheet name="Waterfall" sheetId="4" r:id="rId12"/>
-    <sheet name="Retention" sheetId="5" r:id="rId13"/>
-    <sheet name="Unit Economics" sheetId="6" r:id="rId14"/>
-    <sheet name="Ref" sheetId="7" r:id="rId15"/>
+    <sheet name="2026 Forecast" sheetId="3" r:id="rId7"/>
+    <sheet name="KPI Tracker" sheetId="10" r:id="rId8"/>
+    <sheet name="Waterfall Data" sheetId="11" r:id="rId9"/>
+    <sheet name="Engine" sheetId="8" r:id="rId10"/>
+    <sheet name="Waterfall" sheetId="4" r:id="rId11"/>
+    <sheet name="Retention" sheetId="5" r:id="rId12"/>
+    <sheet name="Unit Economics" sheetId="6" r:id="rId13"/>
+    <sheet name="Ref" sheetId="7" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1334,7 +1333,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="737">
   <si>
     <t>HISTORICAL BASELINE — 2024 &amp; 2025 ACTUALS</t>
   </si>
@@ -3487,27 +3486,12 @@
     <t>CAC Payback (months)</t>
   </si>
   <si>
-    <t>Every month in Q1 had NRR reaching 100%. $180 of expansion MRR from an existing account, combined with zero churn for the second consecutive month, signals that the installed base is healthy and beginning to grow.</t>
-  </si>
-  <si>
-    <t>EBITDA margin improved each month of Q1. 18.9% in January, 20.1% in February, 22.4% in March, each driven by OpEx tracking below forecast and revenue compounding based mostly on fixed cost. The direction is positive, though improvement has come from maintaining low costs rather than outperforming revenue.</t>
-  </si>
-  <si>
     <t>The key watch item for Q2 is new logo conversion. New MRR missed forecast in every month of Q1 ($10,830 actual vs. $12,000 planned) and the March expansion signal came from a single account. If this trend doesn't change, Q2 could face the same issue.</t>
   </si>
   <si>
-    <t>March closed at $153,486 MRR, bringing Q1 total net new MRR to $10,416, which is a 7.3% gain on the opening value of $143,070.</t>
-  </si>
-  <si>
     <t>Q1 Commentary:</t>
   </si>
   <si>
-    <t>Q1 closed with $448,571 in revenue and $91,999 of EBITDA at a 20.5% margin. A solid first quarter, with margins expanding every month as the cost base remained largely fixed against compounding MRR.</t>
-  </si>
-  <si>
-    <t>The unit economics require attention: LTV:CAC of 1.71x is well below the 3x threshold that benchmarks a capital-efficient SaaS business, and CAC Payback of 11.7 months, while under the 12-month early-stage ceiling, leaves little margin for error. Both ratios reflect a business that is acquiring customers at a cost that outpaces the current lifetime value they generate.</t>
-  </si>
-  <si>
     <t>Across the quarter, MRR grew every month (+7.3% overall), EBITDA margin improved steadily, and March produced the first expansion MRR of Q1. The trend is directionally positive, though NRR spent two of three months exactly at 100% with no expansion.</t>
   </si>
   <si>
@@ -3547,14 +3531,26 @@
     <t>← formula: last day of current month</t>
   </si>
   <si>
-    <t>Mar 2026 A vs F</t>
+    <t>Every month in Q1 had NRR reaching 100%. $380 of expansion MRR from an existing account, combined with zero churn for the second consecutive month, signals that the installed base is healthy and beginning to grow.</t>
+  </si>
+  <si>
+    <t>EBITDA margin improved each month of Q1. 18.9% in January, 20.1% in February, 22.5% in March, each driven by OpEx tracking below forecast and revenue compounding based mostly on fixed cost. The direction is positive, though improvement has come from maintaining low costs rather than outperforming revenue.</t>
+  </si>
+  <si>
+    <t>Q1 closed with $448,771 in revenue and $92,139.5 of EBITDA at a 20.5% margin. A solid first quarter, with margins expanding every month as the cost base remained largely fixed against compounding MRR.</t>
+  </si>
+  <si>
+    <t>The unit economics require attention: LTV:CAC of 2.86x is below the 3x threshold that benchmarks a capital-efficient SaaS business, and CAC Payback of 7.03 months is significantly below the 12-month early-stage ceiling, leaves little margin for error. Both ratios reflect a business that is acquiring customers at a cost that outpaces the current lifetime value they generate.</t>
+  </si>
+  <si>
+    <t>March closed at $153,686 MRR, bringing Q1 total net new MRR to $10,616, which is a 7.4% gain on the opening value of $143,070.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="19">
+  <numFmts count="20">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
@@ -3573,7 +3569,8 @@
     <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0.00;\(&quot;$&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="179" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="180" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="183" formatCode="d/mmm/yy"/>
+    <numFmt numFmtId="181" formatCode="d/mmm/yy"/>
+    <numFmt numFmtId="182" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="56" x14ac:knownFonts="1">
     <font>
@@ -4225,7 +4222,7 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4531,17 +4528,7 @@
     <xf numFmtId="0" fontId="27" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="23" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="175" fontId="44" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="44" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -4569,7 +4556,6 @@
     <xf numFmtId="169" fontId="21" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="169" fontId="26" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4577,8 +4563,18 @@
     <xf numFmtId="175" fontId="35" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="175" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="35" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -4977,10 +4973,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5395,19 +5387,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="242">
+      <c r="B1" s="236">
         <v>46023</v>
       </c>
-      <c r="C1" s="242">
+      <c r="C1" s="236">
         <v>46054</v>
       </c>
-      <c r="D1" s="242">
+      <c r="D1" s="236">
         <v>46082</v>
       </c>
-      <c r="E1" s="244">
+      <c r="E1" s="237">
         <v>46113</v>
       </c>
     </row>
@@ -5415,18 +5407,18 @@
       <c r="A2" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="223">
+      <c r="B2" s="217">
         <v>143069.5</v>
       </c>
-      <c r="C2" s="220">
+      <c r="C2" s="214">
         <f>B6</f>
         <v>144779.5</v>
       </c>
-      <c r="D2" s="220">
+      <c r="D2" s="214">
         <f>C6</f>
         <v>150305.5</v>
       </c>
-      <c r="E2" s="245">
+      <c r="E2" s="238">
         <f>D6</f>
         <v>153685.5</v>
       </c>
@@ -5435,16 +5427,16 @@
       <c r="A3" s="123" t="s">
         <v>649</v>
       </c>
-      <c r="B3" s="221">
+      <c r="B3" s="215">
         <v>1710</v>
       </c>
-      <c r="C3" s="221">
+      <c r="C3" s="215">
         <v>6120</v>
       </c>
-      <c r="D3" s="221">
+      <c r="D3" s="215">
         <v>3000</v>
       </c>
-      <c r="E3" s="246">
+      <c r="E3" s="239">
         <v>4200</v>
       </c>
     </row>
@@ -5452,16 +5444,16 @@
       <c r="A4" s="123" t="s">
         <v>650</v>
       </c>
-      <c r="B4" s="221">
-        <v>0</v>
-      </c>
-      <c r="C4" s="221">
-        <v>0</v>
-      </c>
-      <c r="D4" s="221">
+      <c r="B4" s="215">
+        <v>0</v>
+      </c>
+      <c r="C4" s="215">
+        <v>0</v>
+      </c>
+      <c r="D4" s="215">
         <v>380</v>
       </c>
-      <c r="E4" s="246">
+      <c r="E4" s="239">
         <v>750</v>
       </c>
     </row>
@@ -5469,36 +5461,36 @@
       <c r="A5" s="123" t="s">
         <v>652</v>
       </c>
-      <c r="B5" s="221">
-        <v>0</v>
-      </c>
-      <c r="C5" s="221">
+      <c r="B5" s="215">
+        <v>0</v>
+      </c>
+      <c r="C5" s="215">
         <v>594</v>
       </c>
-      <c r="D5" s="221">
-        <v>0</v>
-      </c>
-      <c r="E5" s="246">
+      <c r="D5" s="215">
+        <v>0</v>
+      </c>
+      <c r="E5" s="239">
         <v>1200</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="225" t="s">
+      <c r="A6" s="219" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="226">
+      <c r="B6" s="220">
         <f>B2+B3+B4-B5</f>
         <v>144779.5</v>
       </c>
-      <c r="C6" s="226">
+      <c r="C6" s="220">
         <f>C2+C3+C4-C5</f>
         <v>150305.5</v>
       </c>
-      <c r="D6" s="226">
+      <c r="D6" s="220">
         <f>D2+D3+D4-D5</f>
         <v>153685.5</v>
       </c>
-      <c r="E6" s="226">
+      <c r="E6" s="220">
         <f>E2+E3+E4-E5</f>
         <v>157435.5</v>
       </c>
@@ -5507,16 +5499,16 @@
       <c r="A7" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="221">
+      <c r="B7" s="215">
         <v>30000</v>
       </c>
-      <c r="C7" s="221">
+      <c r="C7" s="215">
         <v>31000</v>
       </c>
-      <c r="D7" s="221">
+      <c r="D7" s="215">
         <v>29000</v>
       </c>
-      <c r="E7" s="246">
+      <c r="E7" s="239">
         <v>31000</v>
       </c>
     </row>
@@ -5524,16 +5516,16 @@
       <c r="A8" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="221">
+      <c r="B8" s="215">
         <v>25000</v>
       </c>
-      <c r="C8" s="221">
+      <c r="C8" s="215">
         <v>25000</v>
       </c>
-      <c r="D8" s="221">
+      <c r="D8" s="215">
         <v>22000</v>
       </c>
-      <c r="E8" s="246">
+      <c r="E8" s="239">
         <v>24000</v>
       </c>
     </row>
@@ -5541,16 +5533,16 @@
       <c r="A9" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="221">
+      <c r="B9" s="215">
         <v>19000</v>
       </c>
-      <c r="C9" s="221">
+      <c r="C9" s="215">
         <v>19000</v>
       </c>
-      <c r="D9" s="221">
+      <c r="D9" s="215">
         <v>22000</v>
       </c>
-      <c r="E9" s="246">
+      <c r="E9" s="239">
         <v>20000</v>
       </c>
     </row>
@@ -5558,19 +5550,19 @@
       <c r="A10" s="124" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="224">
+      <c r="B10" s="218">
         <f>B7+B8+B9</f>
         <v>74000</v>
       </c>
-      <c r="C10" s="224">
+      <c r="C10" s="218">
         <f>C7+C8+C9</f>
         <v>75000</v>
       </c>
-      <c r="D10" s="224">
+      <c r="D10" s="218">
         <f>D7+D8+D9</f>
         <v>73000</v>
       </c>
-      <c r="E10" s="245">
+      <c r="E10" s="238">
         <f>E7+E8+E9</f>
         <v>75000</v>
       </c>
@@ -5579,19 +5571,19 @@
       <c r="A11" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="B11" s="220">
+      <c r="B11" s="214">
         <f>B6*0.3</f>
         <v>43433.85</v>
       </c>
-      <c r="C11" s="220">
+      <c r="C11" s="214">
         <f>C6*0.3</f>
         <v>45091.65</v>
       </c>
-      <c r="D11" s="220">
+      <c r="D11" s="214">
         <f>D6*0.3</f>
         <v>46105.65</v>
       </c>
-      <c r="E11" s="247">
+      <c r="E11" s="240">
         <f>E6*0.3</f>
         <v>47230.65</v>
       </c>
@@ -5600,40 +5592,40 @@
       <c r="A12" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="220">
+      <c r="B12" s="214">
         <f>B6-B11</f>
         <v>101345.65</v>
       </c>
-      <c r="C12" s="220">
+      <c r="C12" s="214">
         <f>C6-C11</f>
         <v>105213.85</v>
       </c>
-      <c r="D12" s="220">
+      <c r="D12" s="214">
         <f>D6-D11</f>
         <v>107579.85</v>
       </c>
-      <c r="E12" s="247">
+      <c r="E12" s="240">
         <f>E6-E11</f>
         <v>110204.85</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="225" t="s">
+      <c r="A13" s="219" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="226">
+      <c r="B13" s="220">
         <f>B12-B10</f>
         <v>27345.649999999994</v>
       </c>
-      <c r="C13" s="226">
+      <c r="C13" s="220">
         <f>C12-C10</f>
         <v>30213.850000000006</v>
       </c>
-      <c r="D13" s="226">
+      <c r="D13" s="220">
         <f>D12-D10</f>
         <v>34579.850000000006</v>
       </c>
-      <c r="E13" s="226">
+      <c r="E13" s="220">
         <f>E12-E10</f>
         <v>35204.850000000006</v>
       </c>
@@ -5642,16 +5634,16 @@
       <c r="A14" s="123" t="s">
         <v>266</v>
       </c>
-      <c r="B14" s="222">
+      <c r="B14" s="216">
         <v>1</v>
       </c>
-      <c r="C14" s="222">
+      <c r="C14" s="216">
         <v>2</v>
       </c>
-      <c r="D14" s="222">
+      <c r="D14" s="216">
         <v>2</v>
       </c>
-      <c r="E14" s="248">
+      <c r="E14" s="241">
         <v>2</v>
       </c>
     </row>
@@ -5659,48 +5651,48 @@
       <c r="A15" s="123" t="s">
         <v>193</v>
       </c>
-      <c r="B15" s="222">
+      <c r="B15" s="216">
         <v>39</v>
       </c>
-      <c r="C15" s="222">
+      <c r="C15" s="216">
         <v>41</v>
       </c>
-      <c r="D15" s="222">
+      <c r="D15" s="216">
         <v>42</v>
       </c>
-      <c r="E15" s="248">
+      <c r="E15" s="241">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="227" t="s">
+      <c r="A16" s="221" t="s">
         <v>194</v>
       </c>
-      <c r="B16" s="228">
+      <c r="B16" s="222">
         <v>52</v>
       </c>
-      <c r="C16" s="228">
+      <c r="C16" s="222">
         <v>53</v>
       </c>
-      <c r="D16" s="228">
+      <c r="D16" s="222">
         <v>54</v>
       </c>
-      <c r="E16" s="228">
+      <c r="E16" s="222">
         <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="42" t="s">
-        <v>726</v>
-      </c>
-      <c r="B18" s="229" t="s">
-        <v>727</v>
-      </c>
-      <c r="C18" s="230" t="s">
-        <v>728</v>
-      </c>
-      <c r="D18" s="231" t="s">
-        <v>729</v>
+        <v>721</v>
+      </c>
+      <c r="B18" s="223" t="s">
+        <v>722</v>
+      </c>
+      <c r="C18" s="224" t="s">
+        <v>723</v>
+      </c>
+      <c r="D18" s="225" t="s">
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -5709,482 +5701,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51A400A-F6A7-4884-99EF-FD343C8B71C2}">
-  <sheetPr>
-    <tabColor theme="8" tint="-0.499984740745262"/>
-  </sheetPr>
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B1" t="s">
-        <v>645</v>
-      </c>
-      <c r="C1" t="s">
-        <v>646</v>
-      </c>
-      <c r="D1" t="s">
-        <v>647</v>
-      </c>
-      <c r="E1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="192">
-        <v>46023</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="100">
-        <f>'Jan 2026 A vs F '!B3</f>
-        <v>143069.5</v>
-      </c>
-      <c r="D2" s="100">
-        <f>'Jan 2026 A vs F '!C3</f>
-        <v>143069.5</v>
-      </c>
-      <c r="E2" s="100">
-        <f>'Jan 2026 A vs F '!D3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="192">
-        <v>46023</v>
-      </c>
-      <c r="B3" t="s">
-        <v>649</v>
-      </c>
-      <c r="C3" s="100">
-        <f>'Jan 2026 A vs F '!B4</f>
-        <v>1710</v>
-      </c>
-      <c r="D3" s="100">
-        <f>'Jan 2026 A vs F '!C4</f>
-        <v>4000</v>
-      </c>
-      <c r="E3" s="100">
-        <f>'Jan 2026 A vs F '!D4</f>
-        <v>-2290</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="192">
-        <v>46023</v>
-      </c>
-      <c r="B4" t="s">
-        <v>650</v>
-      </c>
-      <c r="C4" s="100">
-        <f>'Jan 2026 A vs F '!B5</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="100">
-        <f>'Jan 2026 A vs F '!C5</f>
-        <v>715.34749999999997</v>
-      </c>
-      <c r="E4" s="100">
-        <f>'Jan 2026 A vs F '!D5</f>
-        <v>-715.34749999999997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="192">
-        <v>46023</v>
-      </c>
-      <c r="B5" t="s">
-        <v>651</v>
-      </c>
-      <c r="C5" s="100">
-        <f>'Jan 2026 A vs F '!B6</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="100">
-        <f>'Jan 2026 A vs F '!C6</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="100">
-        <f>C5-D5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="192">
-        <v>46023</v>
-      </c>
-      <c r="B6" t="s">
-        <v>652</v>
-      </c>
-      <c r="C6" s="100">
-        <f>'Jan 2026 A vs F '!B7</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="100">
-        <f>'Jan 2026 A vs F '!C7</f>
-        <v>953.79666666666662</v>
-      </c>
-      <c r="E6" s="168">
-        <f>D6-C6</f>
-        <v>953.79666666666662</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="192">
-        <v>46023</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="100">
-        <f>'Jan 2026 A vs F '!B8</f>
-        <v>1710</v>
-      </c>
-      <c r="D7" s="100">
-        <f>'Jan 2026 A vs F '!C8</f>
-        <v>3761.5508333333332</v>
-      </c>
-      <c r="E7" s="100">
-        <f>'Jan 2026 A vs F '!D8</f>
-        <v>-2051.5508333333332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="192">
-        <v>46023</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="100">
-        <f>'Jan 2026 A vs F '!B9</f>
-        <v>144779.5</v>
-      </c>
-      <c r="D8" s="100">
-        <f>'Jan 2026 A vs F '!C9</f>
-        <v>146831.05083333334</v>
-      </c>
-      <c r="E8" s="100">
-        <f>'Jan 2026 A vs F '!D9</f>
-        <v>-2051.5508333333419</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="192" t="str">
-        <f t="shared" ref="A9:A15" si="0">TEXT(DATE(2026,2,1),"mmm-yy")</f>
-        <v>Feb-26</v>
-      </c>
-      <c r="B9" s="173" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="174">
-        <f>'Feb 2026 A vs F'!B3</f>
-        <v>144779.5</v>
-      </c>
-      <c r="D9" s="174">
-        <f>'Feb 2026 A vs F'!C3</f>
-        <v>146831.04999999999</v>
-      </c>
-      <c r="E9" s="174">
-        <f>C9-D9</f>
-        <v>-2051.5499999999884</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="192" t="str">
-        <f t="shared" si="0"/>
-        <v>Feb-26</v>
-      </c>
-      <c r="B10" s="169" t="s">
-        <v>649</v>
-      </c>
-      <c r="C10" s="171">
-        <f>'Feb 2026 A vs F'!B4</f>
-        <v>6120</v>
-      </c>
-      <c r="D10" s="171">
-        <f>'Feb 2026 A vs F'!C4</f>
-        <v>4000</v>
-      </c>
-      <c r="E10" s="171">
-        <f>C10-D10</f>
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="192" t="str">
-        <f t="shared" si="0"/>
-        <v>Feb-26</v>
-      </c>
-      <c r="B11" s="170" t="s">
-        <v>650</v>
-      </c>
-      <c r="C11" s="168">
-        <f>'Feb 2026 A vs F'!B5</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="168">
-        <f>'Feb 2026 A vs F'!C5</f>
-        <v>715.34749999999997</v>
-      </c>
-      <c r="E11" s="168">
-        <f>C11-D11</f>
-        <v>-715.34749999999997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="192" t="str">
-        <f t="shared" si="0"/>
-        <v>Feb-26</v>
-      </c>
-      <c r="B12" s="169" t="s">
-        <v>651</v>
-      </c>
-      <c r="C12" s="171">
-        <f>'Feb 2026 A vs F'!B6</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="171">
-        <f>'Feb 2026 A vs F'!C6</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="171">
-        <f>D12-C12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="192" t="str">
-        <f t="shared" si="0"/>
-        <v>Feb-26</v>
-      </c>
-      <c r="B13" s="170" t="s">
-        <v>652</v>
-      </c>
-      <c r="C13" s="168">
-        <f>'Feb 2026 A vs F'!B7</f>
-        <v>594</v>
-      </c>
-      <c r="D13" s="168">
-        <f>'Feb 2026 A vs F'!C7</f>
-        <v>953.79666666666662</v>
-      </c>
-      <c r="E13" s="168">
-        <f>D13-C13</f>
-        <v>359.79666666666662</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="192" t="str">
-        <f t="shared" si="0"/>
-        <v>Feb-26</v>
-      </c>
-      <c r="B14" s="169" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="171">
-        <f>'Feb 2026 A vs F'!B8</f>
-        <v>5526</v>
-      </c>
-      <c r="D14" s="171">
-        <f>'Feb 2026 A vs F'!C8</f>
-        <v>3761.5508333333332</v>
-      </c>
-      <c r="E14" s="171">
-        <f>C14-D14</f>
-        <v>1764.4491666666668</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="192" t="str">
-        <f t="shared" si="0"/>
-        <v>Feb-26</v>
-      </c>
-      <c r="B15" s="170" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="168">
-        <f>'Feb 2026 A vs F'!B9</f>
-        <v>150305.5</v>
-      </c>
-      <c r="D15" s="168">
-        <f>'Feb 2026 A vs F'!C9</f>
-        <v>150592.60083333333</v>
-      </c>
-      <c r="E15" s="168">
-        <f>C15-D15</f>
-        <v>-287.10083333333023</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="192" t="str">
-        <f t="shared" ref="A16:A22" si="1">TEXT(DATE(2026,3,1),"mmm-yy")</f>
-        <v>Mar-26</v>
-      </c>
-      <c r="B16" s="189" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="190">
-        <f>'Mar 2026 A vs F'!B3</f>
-        <v>150305.5</v>
-      </c>
-      <c r="D16" s="190">
-        <f>'Mar 2026 A vs F'!C3</f>
-        <v>150592.6</v>
-      </c>
-      <c r="E16" s="191">
-        <f>'Mar 2026 A vs F'!D3</f>
-        <v>-287.10000000000582</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="192" t="str">
-        <f t="shared" si="1"/>
-        <v>Mar-26</v>
-      </c>
-      <c r="B17" s="186" t="s">
-        <v>649</v>
-      </c>
-      <c r="C17" s="187">
-        <f>'Mar 2026 A vs F'!B4</f>
-        <v>3000</v>
-      </c>
-      <c r="D17" s="187">
-        <f>'Mar 2026 A vs F'!C4</f>
-        <v>4000</v>
-      </c>
-      <c r="E17" s="188">
-        <f>'Mar 2026 A vs F'!D4</f>
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="192" t="str">
-        <f t="shared" si="1"/>
-        <v>Mar-26</v>
-      </c>
-      <c r="B18" s="177" t="s">
-        <v>650</v>
-      </c>
-      <c r="C18" s="184">
-        <f>'Mar 2026 A vs F'!B5</f>
-        <v>380</v>
-      </c>
-      <c r="D18" s="184">
-        <f>'Mar 2026 A vs F'!C5</f>
-        <v>715.34749999999997</v>
-      </c>
-      <c r="E18" s="179">
-        <f>'Mar 2026 A vs F'!D5</f>
-        <v>-335.34749999999997</v>
-      </c>
-      <c r="I18" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="192" t="str">
-        <f t="shared" si="1"/>
-        <v>Mar-26</v>
-      </c>
-      <c r="B19" s="182" t="s">
-        <v>651</v>
-      </c>
-      <c r="C19" s="185">
-        <f>'Mar 2026 A vs F'!B6</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="185">
-        <f>'Mar 2026 A vs F'!C6</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="183">
-        <f>D19-C19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="192" t="str">
-        <f t="shared" si="1"/>
-        <v>Mar-26</v>
-      </c>
-      <c r="B20" s="177" t="s">
-        <v>652</v>
-      </c>
-      <c r="C20" s="184">
-        <f>'Mar 2026 A vs F'!B7</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="184">
-        <f>'Mar 2026 A vs F'!C7</f>
-        <v>953.79666666666662</v>
-      </c>
-      <c r="E20" s="179">
-        <f>'Mar 2026 A vs F'!D7</f>
-        <v>953.79666666666662</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="192" t="str">
-        <f t="shared" si="1"/>
-        <v>Mar-26</v>
-      </c>
-      <c r="B21" s="182" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="185">
-        <f>'Mar 2026 A vs F'!B8</f>
-        <v>3380</v>
-      </c>
-      <c r="D21" s="185">
-        <f>'Mar 2026 A vs F'!C8</f>
-        <v>3761.5508333333332</v>
-      </c>
-      <c r="E21" s="183">
-        <f>'Mar 2026 A vs F'!D8</f>
-        <v>-381.55083333333323</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="192" t="str">
-        <f t="shared" si="1"/>
-        <v>Mar-26</v>
-      </c>
-      <c r="B22" s="178" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="181">
-        <f>'Mar 2026 A vs F'!B9</f>
-        <v>153685.5</v>
-      </c>
-      <c r="D22" s="181">
-        <f>'Mar 2026 A vs F'!C9</f>
-        <v>154354.15083333335</v>
-      </c>
-      <c r="E22" s="180">
-        <f>'Mar 2026 A vs F'!D9</f>
-        <v>-668.65083333334769</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{892FC6DE-03E7-4ACC-888F-430CD55F0A58}">
   <dimension ref="A1:V102"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12888,7 +12404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AF1E1DF-5B5C-43E7-99AA-DD09013270A5}">
   <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13857,7 +13373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A21C1A-AA73-416E-A9F6-D8961CE20C9F}">
   <dimension ref="A1:AC37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13988,7 +13504,7 @@
         <f>Waterfall!A29</f>
         <v>46082</v>
       </c>
-      <c r="AC4" s="249">
+      <c r="AC4" s="242">
         <v>46113</v>
       </c>
     </row>
@@ -16308,35 +15824,35 @@
       </c>
     </row>
     <row r="34" spans="1:27" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="215" t="s">
+      <c r="A34" s="246" t="s">
         <v>188</v>
       </c>
-      <c r="B34" s="216"/>
-      <c r="C34" s="216"/>
-      <c r="D34" s="216"/>
-      <c r="E34" s="216"/>
-      <c r="F34" s="216"/>
-      <c r="G34" s="216"/>
-      <c r="H34" s="216"/>
-      <c r="I34" s="216"/>
-      <c r="J34" s="216"/>
-      <c r="K34" s="216"/>
-      <c r="L34" s="216"/>
-      <c r="M34" s="216"/>
-      <c r="N34" s="216"/>
-      <c r="O34" s="216"/>
-      <c r="P34" s="216"/>
-      <c r="Q34" s="216"/>
-      <c r="R34" s="216"/>
-      <c r="S34" s="216"/>
-      <c r="T34" s="216"/>
-      <c r="U34" s="216"/>
-      <c r="V34" s="216"/>
-      <c r="W34" s="216"/>
-      <c r="X34" s="216"/>
-      <c r="Y34" s="216"/>
-      <c r="Z34" s="216"/>
-      <c r="AA34" s="216"/>
+      <c r="B34" s="247"/>
+      <c r="C34" s="247"/>
+      <c r="D34" s="247"/>
+      <c r="E34" s="247"/>
+      <c r="F34" s="247"/>
+      <c r="G34" s="247"/>
+      <c r="H34" s="247"/>
+      <c r="I34" s="247"/>
+      <c r="J34" s="247"/>
+      <c r="K34" s="247"/>
+      <c r="L34" s="247"/>
+      <c r="M34" s="247"/>
+      <c r="N34" s="247"/>
+      <c r="O34" s="247"/>
+      <c r="P34" s="247"/>
+      <c r="Q34" s="247"/>
+      <c r="R34" s="247"/>
+      <c r="S34" s="247"/>
+      <c r="T34" s="247"/>
+      <c r="U34" s="247"/>
+      <c r="V34" s="247"/>
+      <c r="W34" s="247"/>
+      <c r="X34" s="247"/>
+      <c r="Y34" s="247"/>
+      <c r="Z34" s="247"/>
+      <c r="AA34" s="247"/>
     </row>
     <row r="35" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="1:27" x14ac:dyDescent="0.35">
@@ -16345,35 +15861,35 @@
       </c>
     </row>
     <row r="37" spans="1:27" ht="95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="215" t="s">
+      <c r="A37" s="246" t="s">
         <v>190</v>
       </c>
-      <c r="B37" s="216"/>
-      <c r="C37" s="216"/>
-      <c r="D37" s="216"/>
-      <c r="E37" s="216"/>
-      <c r="F37" s="216"/>
-      <c r="G37" s="216"/>
-      <c r="H37" s="216"/>
-      <c r="I37" s="216"/>
-      <c r="J37" s="216"/>
-      <c r="K37" s="216"/>
-      <c r="L37" s="216"/>
-      <c r="M37" s="216"/>
-      <c r="N37" s="216"/>
-      <c r="O37" s="216"/>
-      <c r="P37" s="216"/>
-      <c r="Q37" s="216"/>
-      <c r="R37" s="216"/>
-      <c r="S37" s="216"/>
-      <c r="T37" s="216"/>
-      <c r="U37" s="216"/>
-      <c r="V37" s="216"/>
-      <c r="W37" s="216"/>
-      <c r="X37" s="216"/>
-      <c r="Y37" s="216"/>
-      <c r="Z37" s="216"/>
-      <c r="AA37" s="216"/>
+      <c r="B37" s="247"/>
+      <c r="C37" s="247"/>
+      <c r="D37" s="247"/>
+      <c r="E37" s="247"/>
+      <c r="F37" s="247"/>
+      <c r="G37" s="247"/>
+      <c r="H37" s="247"/>
+      <c r="I37" s="247"/>
+      <c r="J37" s="247"/>
+      <c r="K37" s="247"/>
+      <c r="L37" s="247"/>
+      <c r="M37" s="247"/>
+      <c r="N37" s="247"/>
+      <c r="O37" s="247"/>
+      <c r="P37" s="247"/>
+      <c r="Q37" s="247"/>
+      <c r="R37" s="247"/>
+      <c r="S37" s="247"/>
+      <c r="T37" s="247"/>
+      <c r="U37" s="247"/>
+      <c r="V37" s="247"/>
+      <c r="W37" s="247"/>
+      <c r="X37" s="247"/>
+      <c r="Y37" s="247"/>
+      <c r="Z37" s="247"/>
+      <c r="AA37" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -16385,7 +15901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD2EC7D5-ABE4-462E-B355-560F0DC098E1}">
   <dimension ref="A1:J105"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -17097,18 +16613,18 @@
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A64" s="217" t="s">
+      <c r="A64" s="248" t="s">
         <v>256</v>
       </c>
-      <c r="B64" s="217"/>
-      <c r="C64" s="217"/>
-      <c r="D64" s="217"/>
-      <c r="E64" s="217"/>
-      <c r="F64" s="217"/>
-      <c r="G64" s="217"/>
-      <c r="H64" s="217"/>
-      <c r="I64" s="217"/>
-      <c r="J64" s="217"/>
+      <c r="B64" s="248"/>
+      <c r="C64" s="248"/>
+      <c r="D64" s="248"/>
+      <c r="E64" s="248"/>
+      <c r="F64" s="248"/>
+      <c r="G64" s="248"/>
+      <c r="H64" s="248"/>
+      <c r="I64" s="248"/>
+      <c r="J64" s="248"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="62" t="s">
@@ -17818,7 +17334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4350C285-D3C6-4E27-BA9F-6201C7B9568E}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -19169,30 +18685,30 @@
       <c r="A47" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B47" s="213" t="s">
+      <c r="B47" s="244" t="s">
         <v>311</v>
       </c>
-      <c r="C47" s="213"/>
-      <c r="D47" s="213"/>
-      <c r="E47" s="213"/>
-      <c r="F47" s="213"/>
-      <c r="G47" s="213"/>
-      <c r="H47" s="213"/>
-      <c r="I47" s="213"/>
+      <c r="C47" s="244"/>
+      <c r="D47" s="244"/>
+      <c r="E47" s="244"/>
+      <c r="F47" s="244"/>
+      <c r="G47" s="244"/>
+      <c r="H47" s="244"/>
+      <c r="I47" s="244"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B49" s="213" t="s">
+      <c r="B49" s="244" t="s">
         <v>312</v>
       </c>
-      <c r="C49" s="213"/>
-      <c r="D49" s="213"/>
-      <c r="E49" s="213"/>
-      <c r="F49" s="213"/>
-      <c r="G49" s="213"/>
-      <c r="H49" s="213"/>
+      <c r="C49" s="244"/>
+      <c r="D49" s="244"/>
+      <c r="E49" s="244"/>
+      <c r="F49" s="244"/>
+      <c r="G49" s="244"/>
+      <c r="H49" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -21283,11 +20799,11 @@
       <c r="A1" s="124" t="s">
         <v>600</v>
       </c>
-      <c r="H1" s="232" t="s">
-        <v>730</v>
-      </c>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
+      <c r="H1" s="226" t="s">
+        <v>725</v>
+      </c>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="125" t="s">
@@ -21309,21 +20825,21 @@
       <c r="F2" s="125" t="s">
         <v>602</v>
       </c>
-      <c r="H2" s="234" t="s">
-        <v>731</v>
-      </c>
-      <c r="I2" s="235">
+      <c r="H2" s="228" t="s">
+        <v>726</v>
+      </c>
+      <c r="I2" s="229">
         <v>46082</v>
       </c>
-      <c r="J2" s="236" t="s">
-        <v>732</v>
+      <c r="J2" s="230" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="240">
+      <c r="B3" s="234">
         <f>INDEX(Actuals!$B$2:$Z$2,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
         <v>150305.5</v>
       </c>
@@ -21342,21 +20858,21 @@
         <f t="array" ref="F3">_xlfn.IFS(D3&lt;0, "U", D3&gt;0, "F", D3=0, "-")</f>
         <v>U</v>
       </c>
-      <c r="H3" s="237" t="s">
-        <v>733</v>
-      </c>
-      <c r="I3" s="238" t="s">
-        <v>734</v>
-      </c>
-      <c r="J3" s="236" t="s">
-        <v>732</v>
+      <c r="H3" s="231" t="s">
+        <v>728</v>
+      </c>
+      <c r="I3" s="232" t="s">
+        <v>729</v>
+      </c>
+      <c r="J3" s="230" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="240">
+      <c r="B4" s="234">
         <f>INDEX(Actuals!$B$3:$Z$3,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
         <v>3000</v>
       </c>
@@ -21375,22 +20891,22 @@
         <f t="array" ref="F4">_xlfn.IFS(D4&lt;0, "U", D4&gt;0, "F", D4=0, "-")</f>
         <v>U</v>
       </c>
-      <c r="H4" s="237" t="s">
-        <v>735</v>
-      </c>
-      <c r="I4" s="239">
+      <c r="H4" s="231" t="s">
+        <v>730</v>
+      </c>
+      <c r="I4" s="233">
         <f>EOMONTH(I2,0)</f>
         <v>46112</v>
       </c>
-      <c r="J4" s="236" t="s">
-        <v>736</v>
+      <c r="J4" s="230" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="240">
+      <c r="B5" s="234">
         <f>INDEX(Actuals!$B$4:$Z$4,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
         <v>380</v>
       </c>
@@ -21438,7 +20954,7 @@
       <c r="A7" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="240">
+      <c r="B7" s="234">
         <f>INDEX(Actuals!$B$5:$Z$5,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
         <v>0</v>
       </c>
@@ -21457,6 +20973,10 @@
       <c r="F7" s="133" t="str" cm="1">
         <f t="array" ref="F7">_xlfn.IFS(D7&gt;0, "F", D7&lt;0, "U", D7=0, "-")</f>
         <v>F</v>
+      </c>
+      <c r="J7">
+        <f>INDEX(Actuals!$B$7:$Z$7,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <v>29000</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21683,7 +21203,7 @@
       <c r="A18" s="127" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="219">
+      <c r="B18" s="100">
         <f>INDEX(Actuals!$B$7:$Z$7,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
         <v>29000</v>
       </c>
@@ -21711,7 +21231,7 @@
       <c r="A19" s="127" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="219">
+      <c r="B19" s="100">
         <f>INDEX(Actuals!$B$8:$Z$8,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
         <v>22000</v>
       </c>
@@ -21739,7 +21259,7 @@
       <c r="A20" s="127" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="219">
+      <c r="B20" s="100">
         <f>INDEX(Actuals!$B$9:$Z$9,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
         <v>22000</v>
       </c>
@@ -21852,6 +21372,9 @@
         <v>694</v>
       </c>
     </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="H28" s="249"/>
+    </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="160" t="s">
         <v>4</v>
@@ -21871,7 +21394,7 @@
       <c r="A30" s="123" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="241">
+      <c r="B30" s="235">
         <f>INDEX(Actuals!$B$15:$Z$15,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
         <v>42</v>
       </c>
@@ -21887,7 +21410,7 @@
       <c r="A31" s="123" t="s">
         <v>194</v>
       </c>
-      <c r="B31" s="241">
+      <c r="B31" s="235">
         <f>INDEX(Actuals!$B$16:$Z$16,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
         <v>54</v>
       </c>
@@ -21938,7 +21461,7 @@
       <c r="A34" s="123" t="s">
         <v>620</v>
       </c>
-      <c r="B34" s="243">
+      <c r="B34" s="28">
         <f>INDEX(Retention!$B$6:$AZ$6,MATCH($I$2,Retention!$B$4:$AZ$4,0))</f>
         <v>1</v>
       </c>
@@ -21954,7 +21477,7 @@
       <c r="A35" s="123" t="s">
         <v>622</v>
       </c>
-      <c r="B35" s="243">
+      <c r="B35" s="28">
         <f>INDEX(Retention!$B$7:$AZ$7,MATCH($I$2,Retention!$B$4:$AZ$4,0))</f>
         <v>1.00240271380201</v>
       </c>
@@ -22018,7 +21541,7 @@
       <c r="A39" s="164" t="s">
         <v>664</v>
       </c>
-      <c r="B39" s="241">
+      <c r="B39" s="235">
         <f>INDEX(Actuals!$B$14:$Z$14,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
         <v>2</v>
       </c>
@@ -22194,29 +21717,29 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="250" t="str">
+      <c r="A61" s="243" t="str">
         <f>TEXT($I$2,"mmmm yyyy")&amp;" — Closing MRR: "&amp;TEXT(B9,"$#,##0")&amp;" | NRR: "&amp;TEXT(B35,"0.0%")&amp;" | EBITDA margin: "&amp;TEXT(B23,"0.0%")</f>
         <v>March 2026 — Closing MRR: $153,686 | NRR: 100.2% | EBITDA margin: 22.5%</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="212" t="s">
-        <v>720</v>
+        <v>736</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="212" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="212" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="212" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -22437,27 +21960,27 @@
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" s="210" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" s="212" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" s="212" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" s="212" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" s="212" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>
@@ -22466,968 +21989,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FFBF67-E473-4C22-91A5-16692A5CDF7F}">
-  <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:N65"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="21.81640625" customWidth="1"/>
-    <col min="4" max="4" width="18.1796875" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" customWidth="1"/>
-    <col min="8" max="8" width="36.36328125" customWidth="1"/>
-    <col min="9" max="9" width="14.6328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
-        <v>600</v>
-      </c>
-      <c r="H1" s="232" t="s">
-        <v>730</v>
-      </c>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="125" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="198" t="str">
-        <f>"Actual - "&amp;TEXT($I$2,"mmm yy")</f>
-        <v>Actual - Apr 26</v>
-      </c>
-      <c r="C2" s="125" t="s">
-        <v>675</v>
-      </c>
-      <c r="D2" s="125" t="s">
-        <v>597</v>
-      </c>
-      <c r="E2" s="125" t="s">
-        <v>598</v>
-      </c>
-      <c r="F2" s="125" t="s">
-        <v>602</v>
-      </c>
-      <c r="H2" s="234" t="s">
-        <v>731</v>
-      </c>
-      <c r="I2" s="235">
-        <v>46113</v>
-      </c>
-      <c r="J2" s="236" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="126" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="240">
-        <f>INDEX(Actuals!$B$2:$Z$2,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
-        <v>153685.5</v>
-      </c>
-      <c r="C3" s="128">
-        <v>150592.6</v>
-      </c>
-      <c r="D3" s="128">
-        <f t="shared" ref="D3:D10" si="0">B3-C3</f>
-        <v>3092.8999999999942</v>
-      </c>
-      <c r="E3" s="129">
-        <f>IFERROR(B3/C3-1, 0)</f>
-        <v>2.0538193775789804E-2</v>
-      </c>
-      <c r="F3" s="130" t="str" cm="1">
-        <f t="array" ref="F3">_xlfn.IFS(D3&lt;0, "U", D3&gt;0, "F", D3=0, "-")</f>
-        <v>F</v>
-      </c>
-      <c r="H3" s="237" t="s">
-        <v>733</v>
-      </c>
-      <c r="I3" s="238" t="s">
-        <v>737</v>
-      </c>
-      <c r="J3" s="236" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="158" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="240">
-        <f>INDEX(Actuals!$B$3:$Z$3,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
-        <v>4200</v>
-      </c>
-      <c r="C4" s="128">
-        <v>4000</v>
-      </c>
-      <c r="D4" s="128">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-      <c r="E4" s="129">
-        <f>IFERROR(B4/C4-1, 0)</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="F4" s="130" t="str" cm="1">
-        <f t="array" ref="F4">_xlfn.IFS(D4&lt;0, "U", D4&gt;0, "F", D4=0, "-")</f>
-        <v>F</v>
-      </c>
-      <c r="H4" s="237" t="s">
-        <v>735</v>
-      </c>
-      <c r="I4" s="239">
-        <f>EOMONTH(I2,0)</f>
-        <v>46142</v>
-      </c>
-      <c r="J4" s="236" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="158" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="240">
-        <f>INDEX(Actuals!$B$4:$Z$4,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
-        <v>750</v>
-      </c>
-      <c r="C5" s="128">
-        <f>'2026 Forecast'!B9/3</f>
-        <v>715.34749999999997</v>
-      </c>
-      <c r="D5" s="128">
-        <f t="shared" si="0"/>
-        <v>34.652500000000032</v>
-      </c>
-      <c r="E5" s="129">
-        <f>IFERROR(B5/C5-1, 0)</f>
-        <v>4.8441491722554408E-2</v>
-      </c>
-      <c r="F5" s="130" t="str" cm="1">
-        <f t="array" ref="F5">_xlfn.IFS(D5&lt;0, "U", D5&gt;0, "F", D5=0, "-")</f>
-        <v>F</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="126" t="s">
-        <v>654</v>
-      </c>
-      <c r="B6" s="128">
-        <v>0</v>
-      </c>
-      <c r="C6" s="128">
-        <v>0</v>
-      </c>
-      <c r="D6" s="128">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="129">
-        <f>IFERROR(B6/C6-1, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="130" t="str" cm="1">
-        <f t="array" ref="F6">_xlfn.IFS(D6&lt;0, "U", D6&gt;0, "F", D6=0, "-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="126" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="240">
-        <f>INDEX(Actuals!$B$5:$Z$5,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
-        <v>1200</v>
-      </c>
-      <c r="C7" s="128">
-        <f>'2026 Forecast'!B10/3</f>
-        <v>953.79666666666662</v>
-      </c>
-      <c r="D7" s="128">
-        <f>C7-B7</f>
-        <v>-246.20333333333338</v>
-      </c>
-      <c r="E7" s="129">
-        <f>IFERROR(B7/C7-1, 0)</f>
-        <v>0.25812979006706538</v>
-      </c>
-      <c r="F7" s="133" t="str" cm="1">
-        <f t="array" ref="F7">_xlfn.IFS(D7&gt;0, "F", D7&lt;0, "U", D7=0, "-")</f>
-        <v>U</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="134" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="135">
-        <f>B4+B5-B7</f>
-        <v>3750</v>
-      </c>
-      <c r="C8" s="135">
-        <f>C4+C5-C7</f>
-        <v>3761.5508333333332</v>
-      </c>
-      <c r="D8" s="135">
-        <f t="shared" ref="D8:D15" si="1">B8-C8</f>
-        <v>-11.55083333333323</v>
-      </c>
-      <c r="E8" s="136">
-        <f>B8/C8-1</f>
-        <v>-3.0707635879793083E-3</v>
-      </c>
-      <c r="F8" s="137" t="str" cm="1">
-        <f t="array" ref="F8">_xlfn.IFS(D8&lt;0, "U", D8&gt;0, "F", D8=0, "-")</f>
-        <v>U</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="138" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="139">
-        <f>B3+B4+B5-B7</f>
-        <v>157435.5</v>
-      </c>
-      <c r="C9" s="139">
-        <f>C3+C8</f>
-        <v>154354.15083333335</v>
-      </c>
-      <c r="D9" s="139">
-        <f t="shared" si="1"/>
-        <v>3081.3491666666523</v>
-      </c>
-      <c r="E9" s="140">
-        <f>B9/C9-1</f>
-        <v>1.9962852634872075E-2</v>
-      </c>
-      <c r="F9" s="141" t="str" cm="1">
-        <f t="array" ref="F9">_xlfn.IFS(D9&lt;0, "U", D9&gt;0, "F", D9=0, "-")</f>
-        <v>F</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="127" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="142">
-        <f>B9*12</f>
-        <v>1889226</v>
-      </c>
-      <c r="C10" s="142">
-        <f>C9*12</f>
-        <v>1852249.81</v>
-      </c>
-      <c r="D10" s="142">
-        <f t="shared" si="1"/>
-        <v>36976.189999999944</v>
-      </c>
-      <c r="E10" s="143">
-        <f>B10/C10-1</f>
-        <v>1.9962852634872075E-2</v>
-      </c>
-      <c r="F10" s="144" t="str" cm="1">
-        <f t="array" ref="F10">_xlfn.IFS(D10&lt;0, "U", D10&gt;0, "F", D10=0, "-")</f>
-        <v>F</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="145"/>
-      <c r="B11" s="145"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="127" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="125" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="198" t="str">
-        <f>"Actual - "&amp;TEXT($I$2,"mmm yy")</f>
-        <v>Actual - Apr 26</v>
-      </c>
-      <c r="C13" s="125" t="s">
-        <v>675</v>
-      </c>
-      <c r="D13" s="125" t="s">
-        <v>597</v>
-      </c>
-      <c r="E13" s="125" t="s">
-        <v>598</v>
-      </c>
-      <c r="F13" s="125" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="127" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="131">
-        <f>B9</f>
-        <v>157435.5</v>
-      </c>
-      <c r="C14" s="131">
-        <f>C9</f>
-        <v>154354.15083333335</v>
-      </c>
-      <c r="D14" s="131">
-        <f t="shared" ref="D14:D23" si="2">B14-C14</f>
-        <v>3081.3491666666523</v>
-      </c>
-      <c r="E14" s="132">
-        <f t="shared" ref="E14:E23" si="3">B14/C14-1</f>
-        <v>1.9962852634872075E-2</v>
-      </c>
-      <c r="F14" s="130" t="str" cm="1">
-        <f t="array" ref="F14">_xlfn.IFS(D14&lt;0, "U", D14&gt;0, "F", D14=0, "-")</f>
-        <v>F</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="127" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="131">
-        <f>B14*(1-B17)</f>
-        <v>47230.650000000009</v>
-      </c>
-      <c r="C15" s="131">
-        <f>C14*0.3</f>
-        <v>46306.24525</v>
-      </c>
-      <c r="D15" s="131">
-        <f t="shared" si="2"/>
-        <v>924.40475000000879</v>
-      </c>
-      <c r="E15" s="132">
-        <f t="shared" si="3"/>
-        <v>1.9962852634872297E-2</v>
-      </c>
-      <c r="F15" s="130" t="str" cm="1">
-        <f t="array" ref="F15">_xlfn.IFS(D15&gt;0, "U", D15&lt;0, "F", D15=0, "-")</f>
-        <v>U</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="134" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="146">
-        <f>B14-B15</f>
-        <v>110204.84999999999</v>
-      </c>
-      <c r="C16" s="146">
-        <f>C14-C15</f>
-        <v>108047.90558333334</v>
-      </c>
-      <c r="D16" s="146">
-        <f t="shared" si="2"/>
-        <v>2156.9444166666508</v>
-      </c>
-      <c r="E16" s="147">
-        <f t="shared" si="3"/>
-        <v>1.9962852634872075E-2</v>
-      </c>
-      <c r="F16" s="148" t="str" cm="1">
-        <f t="array" ref="F16">_xlfn.IFS(D16&lt;0, "U", D16&gt;0, "F", D16=0, "-")</f>
-        <v>F</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="138" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="156">
-        <v>0.7</v>
-      </c>
-      <c r="C17" s="155">
-        <f>C16/C14</f>
-        <v>0.7</v>
-      </c>
-      <c r="D17" s="155">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E17" s="155">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="150" t="str" cm="1">
-        <f t="array" ref="F17">_xlfn.IFS(D17&lt;0, "U", D17&gt;0, "F", D17=0, "-")</f>
-        <v>-</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="127" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="219">
-        <f>INDEX(Actuals!$B$7:$Z$7,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
-        <v>31000</v>
-      </c>
-      <c r="C18" s="131">
-        <f>'2026 Forecast'!B25/3</f>
-        <v>30000</v>
-      </c>
-      <c r="D18" s="131">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="E18" s="132">
-        <f t="shared" si="3"/>
-        <v>3.3333333333333437E-2</v>
-      </c>
-      <c r="F18" s="130" t="str" cm="1">
-        <f t="array" ref="F18">_xlfn.IFS(D18&lt;0, "U", D18&gt;0, "F", D18=0, "-")</f>
-        <v>F</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="127" t="s">
-        <v>95</v>
-      </c>
-      <c r="B19" s="219">
-        <f>INDEX(Actuals!$B$8:$Z$8,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
-        <v>24000</v>
-      </c>
-      <c r="C19" s="131">
-        <f>'2026 Forecast'!B26/3</f>
-        <v>25000</v>
-      </c>
-      <c r="D19" s="131">
-        <f t="shared" si="2"/>
-        <v>-1000</v>
-      </c>
-      <c r="E19" s="132">
-        <f t="shared" si="3"/>
-        <v>-4.0000000000000036E-2</v>
-      </c>
-      <c r="F19" s="130" t="str" cm="1">
-        <f t="array" ref="F19">_xlfn.IFS(D19&lt;0, "U", D19&gt;0, "F", D19=0, "-")</f>
-        <v>U</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="127" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="219">
-        <f>INDEX(Actuals!$B$9:$Z$9,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
-        <v>20000</v>
-      </c>
-      <c r="C20" s="131">
-        <f>'2026 Forecast'!B27/3</f>
-        <v>19000</v>
-      </c>
-      <c r="D20" s="131">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="E20" s="132">
-        <f t="shared" si="3"/>
-        <v>5.2631578947368363E-2</v>
-      </c>
-      <c r="F20" s="130" t="str" cm="1">
-        <f t="array" ref="F20">_xlfn.IFS(D20&lt;0, "U", D20&gt;0, "F", D20=0, "-")</f>
-        <v>F</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="134" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="146">
-        <f>SUM(B18:B20)</f>
-        <v>75000</v>
-      </c>
-      <c r="C21" s="146">
-        <f>'2026 Forecast'!B28/3</f>
-        <v>74000</v>
-      </c>
-      <c r="D21" s="146">
-        <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="E21" s="149">
-        <f t="shared" si="3"/>
-        <v>1.3513513513513598E-2</v>
-      </c>
-      <c r="F21" s="148" t="str" cm="1">
-        <f t="array" ref="F21">_xlfn.IFS(D21&lt;0, "U", D21&gt;0, "F", D21=0, "-")</f>
-        <v>F</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="151" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="152">
-        <f>B16-B21</f>
-        <v>35204.849999999991</v>
-      </c>
-      <c r="C22" s="152">
-        <f>C16-C21</f>
-        <v>34047.90558333334</v>
-      </c>
-      <c r="D22" s="152">
-        <f t="shared" si="2"/>
-        <v>1156.9444166666508</v>
-      </c>
-      <c r="E22" s="153">
-        <f t="shared" si="3"/>
-        <v>3.3979899698528993E-2</v>
-      </c>
-      <c r="F22" s="154" t="str" cm="1">
-        <f t="array" ref="F22">_xlfn.IFS(D22&lt;0, "U", D22&gt;0, "F", D22=0, "-")</f>
-        <v>F</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="127" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="162">
-        <f>B22/B14</f>
-        <v>0.22361443257715058</v>
-      </c>
-      <c r="C23" s="162">
-        <f>C22/C14</f>
-        <v>0.22058302546134426</v>
-      </c>
-      <c r="D23" s="132">
-        <f t="shared" si="2"/>
-        <v>3.0314071158063227E-3</v>
-      </c>
-      <c r="E23" s="132">
-        <f t="shared" si="3"/>
-        <v>1.3742703498903497E-2</v>
-      </c>
-      <c r="F23" s="130" t="str" cm="1">
-        <f t="array" ref="F23">IFERROR(_xlfn.IFS(D23&lt;0, "U", D23&gt;0, "F", D23=0, "-"), "-")</f>
-        <v>F</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="157"/>
-    </row>
-    <row r="27" spans="1:14" ht="17" x14ac:dyDescent="0.4">
-      <c r="A27" s="159" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="160" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="160" t="s">
-        <v>283</v>
-      </c>
-      <c r="C29" s="113" t="str">
-        <f>"vs "&amp;TEXT(EOMONTH($I$2,-1),"mmm yyyy")</f>
-        <v>vs Mar 2026</v>
-      </c>
-      <c r="D29" s="160" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="123" t="s">
-        <v>193</v>
-      </c>
-      <c r="B30" s="241">
-        <f>INDEX(Actuals!$B$15:$Z$15,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
-        <v>44</v>
-      </c>
-      <c r="C30" s="123">
-        <f>IFERROR(B30-_xlfn.XLOOKUP("Active Customers",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$C$4:$C$16),"—")</f>
-        <v>3</v>
-      </c>
-      <c r="D30" s="123" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="123" t="s">
-        <v>194</v>
-      </c>
-      <c r="B31" s="241">
-        <f>INDEX(Actuals!$B$16:$Z$16,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
-        <v>56</v>
-      </c>
-      <c r="C31" s="167">
-        <f>B31-INDEX(Actuals!$B$16:$Z$16,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0))</f>
-        <v>2</v>
-      </c>
-      <c r="D31" s="123" t="s">
-        <v>677</v>
-      </c>
-      <c r="N31" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="123" t="s">
-        <v>616</v>
-      </c>
-      <c r="B32" s="131">
-        <f>B9/B30</f>
-        <v>3578.0795454545455</v>
-      </c>
-      <c r="C32" s="131">
-        <f>IFERROR(B32-INDEX(Actuals!$B$6:$Z$6,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0))/INDEX(Actuals!$B$15:$Z$15,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0)),"—")</f>
-        <v>-81.099025974026063</v>
-      </c>
-      <c r="D32" s="123" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A33" s="123" t="s">
-        <v>618</v>
-      </c>
-      <c r="B33" s="162">
-        <f>B17</f>
-        <v>0.7</v>
-      </c>
-      <c r="C33" s="162">
-        <f>0</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="123" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A34" s="123" t="s">
-        <v>620</v>
-      </c>
-      <c r="B34" s="243">
-        <f>INDEX(Retention!$B$6:$AZ$6,MATCH($I$2,Retention!$B$4:$AZ$4,0))</f>
-        <v>1</v>
-      </c>
-      <c r="C34" s="162">
-        <f>B34-INDEX(Retention!$B$6:$AZ$6,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Retention!$B$4:$AZ$4,0))</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="123" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A35" s="123" t="s">
-        <v>622</v>
-      </c>
-      <c r="B35" s="243">
-        <f>INDEX(Retention!$B$7:$AZ$7,MATCH($I$2,Retention!$B$4:$AZ$4,0))</f>
-        <v>1.0049999999999999</v>
-      </c>
-      <c r="C35" s="162">
-        <f>B35-INDEX(Retention!$B$7:$AZ$7,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Retention!$B$4:$AZ$4,0))</f>
-        <v>2.5972861979899342E-3</v>
-      </c>
-      <c r="D35" s="123" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A36" s="123" t="s">
-        <v>623</v>
-      </c>
-      <c r="B36" s="123">
-        <f>IFERROR(IF((B6+B7)=0,"N/A — no losses",(B4+B5)/(B6+B7)),"N/A")</f>
-        <v>4.125</v>
-      </c>
-      <c r="C36" s="123">
-        <f>IFERROR(IF(ISNUMBER(B36),B36-_xlfn.XLOOKUP("Quick Ratio",'KPI Tracker'!$A$4:$A$16,'KPI Tracker'!$B$4:$B$16),"—"),"—")</f>
-        <v>4.125</v>
-      </c>
-      <c r="D36" s="123" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A37" s="123" t="s">
-        <v>625</v>
-      </c>
-      <c r="B37" s="163">
-        <f>B18</f>
-        <v>31000</v>
-      </c>
-      <c r="C37" s="163">
-        <f>B37-INDEX(Actuals!$B$7:$Z$7,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0))</f>
-        <v>2000</v>
-      </c>
-      <c r="D37" s="123" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A38" s="123" t="s">
-        <v>627</v>
-      </c>
-      <c r="B38" s="163">
-        <f>IFERROR(IF(B39=0,"—",B37/B39),"—")</f>
-        <v>15500</v>
-      </c>
-      <c r="C38" s="163">
-        <f>IFERROR(B38-INDEX(Actuals!$B$7:$Z$7,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0))/INDEX(Actuals!$B$14:$Z$14,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0)),"—")</f>
-        <v>1000</v>
-      </c>
-      <c r="D38" s="123" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A39" s="164" t="s">
-        <v>664</v>
-      </c>
-      <c r="B39" s="241">
-        <f>INDEX(Actuals!$B$14:$Z$14,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
-        <v>2</v>
-      </c>
-      <c r="C39" s="123" t="s">
-        <v>629</v>
-      </c>
-      <c r="D39" s="164" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A40" s="123" t="s">
-        <v>659</v>
-      </c>
-      <c r="B40" s="163">
-        <f>IFERROR(IF(('Jan 2026 A vs F '!B46/'Jan 2026 A vs F '!B47+'Feb 2026 A vs F'!B39+B39)=0,"—",('Jan 2026 A vs F '!B46+'Feb 2026 A vs F'!B37+B37)/('Jan 2026 A vs F '!B46/'Jan 2026 A vs F '!B47+'Feb 2026 A vs F'!B39+B39)),"—")</f>
-        <v>18400</v>
-      </c>
-      <c r="C40" s="123" t="s">
-        <v>629</v>
-      </c>
-      <c r="D40" s="123" t="s">
-        <v>663</v>
-      </c>
-      <c r="K40" s="211"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A41" s="123" t="s">
-        <v>628</v>
-      </c>
-      <c r="B41" s="123" t="s">
-        <v>629</v>
-      </c>
-      <c r="C41" s="123" t="s">
-        <v>629</v>
-      </c>
-      <c r="D41" s="123" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A42" s="123" t="s">
-        <v>631</v>
-      </c>
-      <c r="B42" s="123" t="s">
-        <v>629</v>
-      </c>
-      <c r="C42" s="123" t="s">
-        <v>629</v>
-      </c>
-      <c r="D42" s="123" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A43" s="123" t="s">
-        <v>632</v>
-      </c>
-      <c r="B43" s="123" t="s">
-        <v>629</v>
-      </c>
-      <c r="C43" s="123" t="s">
-        <v>629</v>
-      </c>
-      <c r="D43" s="123" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A44" s="165" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A45" s="165" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A47" s="165" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A48" s="165" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A51" s="166" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="160" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="160" t="s">
-        <v>639</v>
-      </c>
-      <c r="C53" s="160" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="123" t="s">
-        <v>616</v>
-      </c>
-      <c r="B54" s="131">
-        <f>B32</f>
-        <v>3578.0795454545455</v>
-      </c>
-      <c r="C54" s="131">
-        <f>B9/B30</f>
-        <v>3578.0795454545455</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="123" t="s">
-        <v>620</v>
-      </c>
-      <c r="B55" s="162">
-        <f>B34</f>
-        <v>1</v>
-      </c>
-      <c r="C55" s="162">
-        <f>Retention!AA6</f>
-        <v>0.99610819735501566</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="123" t="s">
-        <v>622</v>
-      </c>
-      <c r="B56" s="162">
-        <f>B35</f>
-        <v>1.0049999999999999</v>
-      </c>
-      <c r="C56" s="162">
-        <f>Retention!AA7</f>
-        <v>0.99610819735501566</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="123" t="s">
-        <v>623</v>
-      </c>
-      <c r="B57" s="123">
-        <f>B36</f>
-        <v>4.125</v>
-      </c>
-      <c r="C57" s="123">
-        <f>IFERROR(IF((B6+B7)=0,"N/A — no losses",(B4+B5)/(B6+B7)),"N/A")</f>
-        <v>4.125</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="123" t="s">
-        <v>640</v>
-      </c>
-      <c r="B58" s="163">
-        <f>B38</f>
-        <v>15500</v>
-      </c>
-      <c r="C58" s="163">
-        <f>IFERROR(IF(B39=0,"—",B37/B39),"—")</f>
-        <v>15500</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="124" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="250" t="str">
-        <f>TEXT($I$2,"mmmm yyyy")&amp;" — Closing MRR: "&amp;TEXT(B9,"$#,##0")&amp;" | NRR: "&amp;TEXT(B35,"0.0%")&amp;" | EBITDA margin: "&amp;TEXT(B23,"0.0%")</f>
-        <v>April 2026 — Closing MRR: $157,436 | NRR: 100.5% | EBITDA margin: 22.4%</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="212" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="212" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="212" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="212" t="s">
-        <v>719</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -24303,7 +22864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2906536-E0F1-4975-A641-B712DF8BD68D}">
   <sheetPr>
     <tabColor theme="9" tint="-0.499984740745262"/>
@@ -24579,11 +23140,11 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="214" t="s">
+      <c r="A18" s="245" t="s">
         <v>644</v>
       </c>
-      <c r="B18" s="214"/>
-      <c r="C18" s="214"/>
+      <c r="B18" s="245"/>
+      <c r="C18" s="245"/>
       <c r="D18" s="122"/>
       <c r="E18" s="122"/>
     </row>
@@ -24596,4 +23157,480 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51A400A-F6A7-4884-99EF-FD343C8B71C2}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" t="s">
+        <v>645</v>
+      </c>
+      <c r="C1" t="s">
+        <v>646</v>
+      </c>
+      <c r="D1" t="s">
+        <v>647</v>
+      </c>
+      <c r="E1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="192">
+        <v>46023</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="100">
+        <f>'Jan 2026 A vs F '!B3</f>
+        <v>143069.5</v>
+      </c>
+      <c r="D2" s="100">
+        <f>'Jan 2026 A vs F '!C3</f>
+        <v>143069.5</v>
+      </c>
+      <c r="E2" s="100">
+        <f>'Jan 2026 A vs F '!D3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="192">
+        <v>46023</v>
+      </c>
+      <c r="B3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C3" s="100">
+        <f>'Jan 2026 A vs F '!B4</f>
+        <v>1710</v>
+      </c>
+      <c r="D3" s="100">
+        <f>'Jan 2026 A vs F '!C4</f>
+        <v>4000</v>
+      </c>
+      <c r="E3" s="100">
+        <f>'Jan 2026 A vs F '!D4</f>
+        <v>-2290</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="192">
+        <v>46023</v>
+      </c>
+      <c r="B4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C4" s="100">
+        <f>'Jan 2026 A vs F '!B5</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="100">
+        <f>'Jan 2026 A vs F '!C5</f>
+        <v>715.34749999999997</v>
+      </c>
+      <c r="E4" s="100">
+        <f>'Jan 2026 A vs F '!D5</f>
+        <v>-715.34749999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="192">
+        <v>46023</v>
+      </c>
+      <c r="B5" t="s">
+        <v>651</v>
+      </c>
+      <c r="C5" s="100">
+        <f>'Jan 2026 A vs F '!B6</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="100">
+        <f>'Jan 2026 A vs F '!C6</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="100">
+        <f>C5-D5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="192">
+        <v>46023</v>
+      </c>
+      <c r="B6" t="s">
+        <v>652</v>
+      </c>
+      <c r="C6" s="100">
+        <f>'Jan 2026 A vs F '!B7</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="100">
+        <f>'Jan 2026 A vs F '!C7</f>
+        <v>953.79666666666662</v>
+      </c>
+      <c r="E6" s="168">
+        <f>D6-C6</f>
+        <v>953.79666666666662</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="192">
+        <v>46023</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="100">
+        <f>'Jan 2026 A vs F '!B8</f>
+        <v>1710</v>
+      </c>
+      <c r="D7" s="100">
+        <f>'Jan 2026 A vs F '!C8</f>
+        <v>3761.5508333333332</v>
+      </c>
+      <c r="E7" s="100">
+        <f>'Jan 2026 A vs F '!D8</f>
+        <v>-2051.5508333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="192">
+        <v>46023</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="100">
+        <f>'Jan 2026 A vs F '!B9</f>
+        <v>144779.5</v>
+      </c>
+      <c r="D8" s="100">
+        <f>'Jan 2026 A vs F '!C9</f>
+        <v>146831.05083333334</v>
+      </c>
+      <c r="E8" s="100">
+        <f>'Jan 2026 A vs F '!D9</f>
+        <v>-2051.5508333333419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="192" t="str">
+        <f t="shared" ref="A9:A15" si="0">TEXT(DATE(2026,2,1),"mmm-yy")</f>
+        <v>Feb-26</v>
+      </c>
+      <c r="B9" s="173" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="174">
+        <f>'Feb 2026 A vs F'!B3</f>
+        <v>144779.5</v>
+      </c>
+      <c r="D9" s="174">
+        <f>'Feb 2026 A vs F'!C3</f>
+        <v>146831.04999999999</v>
+      </c>
+      <c r="E9" s="174">
+        <f>C9-D9</f>
+        <v>-2051.5499999999884</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="192" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B10" s="169" t="s">
+        <v>649</v>
+      </c>
+      <c r="C10" s="171">
+        <f>'Feb 2026 A vs F'!B4</f>
+        <v>6120</v>
+      </c>
+      <c r="D10" s="171">
+        <f>'Feb 2026 A vs F'!C4</f>
+        <v>4000</v>
+      </c>
+      <c r="E10" s="171">
+        <f>C10-D10</f>
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="192" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B11" s="170" t="s">
+        <v>650</v>
+      </c>
+      <c r="C11" s="168">
+        <f>'Feb 2026 A vs F'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="168">
+        <f>'Feb 2026 A vs F'!C5</f>
+        <v>715.34749999999997</v>
+      </c>
+      <c r="E11" s="168">
+        <f>C11-D11</f>
+        <v>-715.34749999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="192" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B12" s="169" t="s">
+        <v>651</v>
+      </c>
+      <c r="C12" s="171">
+        <f>'Feb 2026 A vs F'!B6</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="171">
+        <f>'Feb 2026 A vs F'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="171">
+        <f>D12-C12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="192" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>652</v>
+      </c>
+      <c r="C13" s="168">
+        <f>'Feb 2026 A vs F'!B7</f>
+        <v>594</v>
+      </c>
+      <c r="D13" s="168">
+        <f>'Feb 2026 A vs F'!C7</f>
+        <v>953.79666666666662</v>
+      </c>
+      <c r="E13" s="168">
+        <f>D13-C13</f>
+        <v>359.79666666666662</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="192" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B14" s="169" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="171">
+        <f>'Feb 2026 A vs F'!B8</f>
+        <v>5526</v>
+      </c>
+      <c r="D14" s="171">
+        <f>'Feb 2026 A vs F'!C8</f>
+        <v>3761.5508333333332</v>
+      </c>
+      <c r="E14" s="171">
+        <f>C14-D14</f>
+        <v>1764.4491666666668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="192" t="str">
+        <f t="shared" si="0"/>
+        <v>Feb-26</v>
+      </c>
+      <c r="B15" s="170" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="168">
+        <f>'Feb 2026 A vs F'!B9</f>
+        <v>150305.5</v>
+      </c>
+      <c r="D15" s="168">
+        <f>'Feb 2026 A vs F'!C9</f>
+        <v>150592.60083333333</v>
+      </c>
+      <c r="E15" s="168">
+        <f>C15-D15</f>
+        <v>-287.10083333333023</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="192" t="str">
+        <f t="shared" ref="A16:A22" si="1">TEXT(DATE(2026,3,1),"mmm-yy")</f>
+        <v>Mar-26</v>
+      </c>
+      <c r="B16" s="189" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="190">
+        <f>'Mar 2026 A vs F'!B3</f>
+        <v>150305.5</v>
+      </c>
+      <c r="D16" s="190">
+        <f>'Mar 2026 A vs F'!C3</f>
+        <v>150592.6</v>
+      </c>
+      <c r="E16" s="191">
+        <f>'Mar 2026 A vs F'!D3</f>
+        <v>-287.10000000000582</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="192" t="str">
+        <f t="shared" si="1"/>
+        <v>Mar-26</v>
+      </c>
+      <c r="B17" s="186" t="s">
+        <v>649</v>
+      </c>
+      <c r="C17" s="187">
+        <f>'Mar 2026 A vs F'!B4</f>
+        <v>3000</v>
+      </c>
+      <c r="D17" s="187">
+        <f>'Mar 2026 A vs F'!C4</f>
+        <v>4000</v>
+      </c>
+      <c r="E17" s="188">
+        <f>'Mar 2026 A vs F'!D4</f>
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="192" t="str">
+        <f t="shared" si="1"/>
+        <v>Mar-26</v>
+      </c>
+      <c r="B18" s="177" t="s">
+        <v>650</v>
+      </c>
+      <c r="C18" s="184">
+        <f>'Mar 2026 A vs F'!B5</f>
+        <v>380</v>
+      </c>
+      <c r="D18" s="184">
+        <f>'Mar 2026 A vs F'!C5</f>
+        <v>715.34749999999997</v>
+      </c>
+      <c r="E18" s="179">
+        <f>'Mar 2026 A vs F'!D5</f>
+        <v>-335.34749999999997</v>
+      </c>
+      <c r="I18" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="192" t="str">
+        <f t="shared" si="1"/>
+        <v>Mar-26</v>
+      </c>
+      <c r="B19" s="182" t="s">
+        <v>651</v>
+      </c>
+      <c r="C19" s="185">
+        <f>'Mar 2026 A vs F'!B6</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="185">
+        <f>'Mar 2026 A vs F'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="183">
+        <f>D19-C19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="192" t="str">
+        <f t="shared" si="1"/>
+        <v>Mar-26</v>
+      </c>
+      <c r="B20" s="177" t="s">
+        <v>652</v>
+      </c>
+      <c r="C20" s="184">
+        <f>'Mar 2026 A vs F'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="184">
+        <f>'Mar 2026 A vs F'!C7</f>
+        <v>953.79666666666662</v>
+      </c>
+      <c r="E20" s="179">
+        <f>'Mar 2026 A vs F'!D7</f>
+        <v>953.79666666666662</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="192" t="str">
+        <f t="shared" si="1"/>
+        <v>Mar-26</v>
+      </c>
+      <c r="B21" s="182" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="185">
+        <f>'Mar 2026 A vs F'!B8</f>
+        <v>3380</v>
+      </c>
+      <c r="D21" s="185">
+        <f>'Mar 2026 A vs F'!C8</f>
+        <v>3761.5508333333332</v>
+      </c>
+      <c r="E21" s="183">
+        <f>'Mar 2026 A vs F'!D8</f>
+        <v>-381.55083333333323</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="192" t="str">
+        <f t="shared" si="1"/>
+        <v>Mar-26</v>
+      </c>
+      <c r="B22" s="178" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="181">
+        <f>'Mar 2026 A vs F'!B9</f>
+        <v>153685.5</v>
+      </c>
+      <c r="D22" s="181">
+        <f>'Mar 2026 A vs F'!C9</f>
+        <v>154354.15083333335</v>
+      </c>
+      <c r="E22" s="180">
+        <f>'Mar 2026 A vs F'!D9</f>
+        <v>-668.65083333334769</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/submissions/excel/excel_09_workbook_redesign.xlsx
+++ b/submissions/excel/excel_09_workbook_redesign.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\venti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28D0AF6-BCC9-4753-AC1D-5F90AD48DFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1B7E1B-59F7-4178-B3F0-A7C4240D5171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1333,7 +1333,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="738">
   <si>
     <t>HISTORICAL BASELINE — 2024 &amp; 2025 ACTUALS</t>
   </si>
@@ -3544,13 +3544,16 @@
   </si>
   <si>
     <t>March closed at $153,686 MRR, bringing Q1 total net new MRR to $10,616, which is a 7.4% gain on the opening value of $143,070.</t>
+  </si>
+  <si>
+    <t>INDEX(Retention!$B$6:$AZ$6,MATCH($I$2,Retention!$B$4:$AZ$4,0))</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="20">
+  <numFmts count="19">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
@@ -3569,7 +3572,6 @@
     <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0.00;\(&quot;$&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="179" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="180" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="181" formatCode="d/mmm/yy"/>
     <numFmt numFmtId="182" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="56" x14ac:knownFonts="1">
@@ -4222,7 +4224,7 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4556,15 +4558,8 @@
     <xf numFmtId="169" fontId="21" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="26" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="27" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="175" fontId="35" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="175" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="35" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="29" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="36" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -4574,7 +4569,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -5376,17 +5370,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280EEDB7-8B1A-4D96-B70C-C183AB1D0677}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="213" t="s">
         <v>4</v>
       </c>
@@ -5399,11 +5392,8 @@
       <c r="D1" s="236">
         <v>46082</v>
       </c>
-      <c r="E1" s="237">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="123" t="s">
         <v>14</v>
       </c>
@@ -5418,12 +5408,8 @@
         <f>C6</f>
         <v>150305.5</v>
       </c>
-      <c r="E2" s="238">
-        <f>D6</f>
-        <v>153685.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="123" t="s">
         <v>649</v>
       </c>
@@ -5436,11 +5422,8 @@
       <c r="D3" s="215">
         <v>3000</v>
       </c>
-      <c r="E3" s="239">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="123" t="s">
         <v>650</v>
       </c>
@@ -5453,11 +5436,8 @@
       <c r="D4" s="215">
         <v>380</v>
       </c>
-      <c r="E4" s="239">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="123" t="s">
         <v>652</v>
       </c>
@@ -5470,11 +5450,8 @@
       <c r="D5" s="215">
         <v>0</v>
       </c>
-      <c r="E5" s="239">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="219" t="s">
         <v>26</v>
       </c>
@@ -5490,12 +5467,8 @@
         <f>D2+D3+D4-D5</f>
         <v>153685.5</v>
       </c>
-      <c r="E6" s="220">
-        <f>E2+E3+E4-E5</f>
-        <v>157435.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="123" t="s">
         <v>46</v>
       </c>
@@ -5508,11 +5481,8 @@
       <c r="D7" s="215">
         <v>29000</v>
       </c>
-      <c r="E7" s="239">
-        <v>31000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="123" t="s">
         <v>48</v>
       </c>
@@ -5525,11 +5495,8 @@
       <c r="D8" s="215">
         <v>22000</v>
       </c>
-      <c r="E8" s="239">
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="123" t="s">
         <v>50</v>
       </c>
@@ -5542,11 +5509,8 @@
       <c r="D9" s="215">
         <v>22000</v>
       </c>
-      <c r="E9" s="239">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="124" t="s">
         <v>51</v>
       </c>
@@ -5562,12 +5526,8 @@
         <f>D7+D8+D9</f>
         <v>73000</v>
       </c>
-      <c r="E10" s="238">
-        <f>E7+E8+E9</f>
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="123" t="s">
         <v>119</v>
       </c>
@@ -5583,12 +5543,8 @@
         <f>D6*0.3</f>
         <v>46105.65</v>
       </c>
-      <c r="E11" s="240">
-        <f>E6*0.3</f>
-        <v>47230.65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="123" t="s">
         <v>42</v>
       </c>
@@ -5604,12 +5560,8 @@
         <f>D6-D11</f>
         <v>107579.85</v>
       </c>
-      <c r="E12" s="240">
-        <f>E6-E11</f>
-        <v>110204.85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="219" t="s">
         <v>53</v>
       </c>
@@ -5625,12 +5577,8 @@
         <f>D12-D10</f>
         <v>34579.850000000006</v>
       </c>
-      <c r="E13" s="220">
-        <f>E12-E10</f>
-        <v>35204.850000000006</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="123" t="s">
         <v>266</v>
       </c>
@@ -5643,11 +5591,8 @@
       <c r="D14" s="216">
         <v>2</v>
       </c>
-      <c r="E14" s="241">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="123" t="s">
         <v>193</v>
       </c>
@@ -5660,11 +5605,8 @@
       <c r="D15" s="216">
         <v>42</v>
       </c>
-      <c r="E15" s="241">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="221" t="s">
         <v>194</v>
       </c>
@@ -5676,9 +5618,6 @@
       </c>
       <c r="D16" s="222">
         <v>54</v>
-      </c>
-      <c r="E16" s="222">
-        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -13375,24 +13314,24 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A21C1A-AA73-416E-A9F6-D8961CE20C9F}">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AB37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="28" max="28" width="12.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="41" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" s="42" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" s="42" t="s">
         <v>155</v>
       </c>
@@ -13504,11 +13443,8 @@
         <f>Waterfall!A29</f>
         <v>46082</v>
       </c>
-      <c r="AC4" s="242">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" s="42" t="s">
         <v>14</v>
       </c>
@@ -13621,7 +13557,7 @@
         <v>158154.5</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" s="42" t="s">
         <v>168</v>
       </c>
@@ -13733,11 +13669,8 @@
         <f>IF(Waterfall!B29=0,"-",1+(Waterfall!E29+Waterfall!F29)/Waterfall!B29)</f>
         <v>1</v>
       </c>
-      <c r="AC6" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" s="42" t="s">
         <v>169</v>
       </c>
@@ -13849,16 +13782,13 @@
         <f>IF(Waterfall!B29=0,"-",1+(Waterfall!D29+Waterfall!E29+Waterfall!F29)/Waterfall!B29)</f>
         <v>1.00240271380201</v>
       </c>
-      <c r="AC7" s="28">
-        <v>1.0049999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" s="42" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" s="42" t="s">
         <v>155</v>
       </c>
@@ -13971,7 +13901,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" s="42" t="s">
         <v>171</v>
       </c>
@@ -14084,7 +14014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" s="42" t="s">
         <v>172</v>
       </c>
@@ -14197,12 +14127,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" s="42" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" s="42" t="s">
         <v>155</v>
       </c>
@@ -14315,7 +14245,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16" s="42" t="s">
         <v>174</v>
       </c>
@@ -15824,35 +15754,35 @@
       </c>
     </row>
     <row r="34" spans="1:27" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="246" t="s">
+      <c r="A34" s="241" t="s">
         <v>188</v>
       </c>
-      <c r="B34" s="247"/>
-      <c r="C34" s="247"/>
-      <c r="D34" s="247"/>
-      <c r="E34" s="247"/>
-      <c r="F34" s="247"/>
-      <c r="G34" s="247"/>
-      <c r="H34" s="247"/>
-      <c r="I34" s="247"/>
-      <c r="J34" s="247"/>
-      <c r="K34" s="247"/>
-      <c r="L34" s="247"/>
-      <c r="M34" s="247"/>
-      <c r="N34" s="247"/>
-      <c r="O34" s="247"/>
-      <c r="P34" s="247"/>
-      <c r="Q34" s="247"/>
-      <c r="R34" s="247"/>
-      <c r="S34" s="247"/>
-      <c r="T34" s="247"/>
-      <c r="U34" s="247"/>
-      <c r="V34" s="247"/>
-      <c r="W34" s="247"/>
-      <c r="X34" s="247"/>
-      <c r="Y34" s="247"/>
-      <c r="Z34" s="247"/>
-      <c r="AA34" s="247"/>
+      <c r="B34" s="242"/>
+      <c r="C34" s="242"/>
+      <c r="D34" s="242"/>
+      <c r="E34" s="242"/>
+      <c r="F34" s="242"/>
+      <c r="G34" s="242"/>
+      <c r="H34" s="242"/>
+      <c r="I34" s="242"/>
+      <c r="J34" s="242"/>
+      <c r="K34" s="242"/>
+      <c r="L34" s="242"/>
+      <c r="M34" s="242"/>
+      <c r="N34" s="242"/>
+      <c r="O34" s="242"/>
+      <c r="P34" s="242"/>
+      <c r="Q34" s="242"/>
+      <c r="R34" s="242"/>
+      <c r="S34" s="242"/>
+      <c r="T34" s="242"/>
+      <c r="U34" s="242"/>
+      <c r="V34" s="242"/>
+      <c r="W34" s="242"/>
+      <c r="X34" s="242"/>
+      <c r="Y34" s="242"/>
+      <c r="Z34" s="242"/>
+      <c r="AA34" s="242"/>
     </row>
     <row r="35" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="1:27" x14ac:dyDescent="0.35">
@@ -15861,35 +15791,35 @@
       </c>
     </row>
     <row r="37" spans="1:27" ht="95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="246" t="s">
+      <c r="A37" s="241" t="s">
         <v>190</v>
       </c>
-      <c r="B37" s="247"/>
-      <c r="C37" s="247"/>
-      <c r="D37" s="247"/>
-      <c r="E37" s="247"/>
-      <c r="F37" s="247"/>
-      <c r="G37" s="247"/>
-      <c r="H37" s="247"/>
-      <c r="I37" s="247"/>
-      <c r="J37" s="247"/>
-      <c r="K37" s="247"/>
-      <c r="L37" s="247"/>
-      <c r="M37" s="247"/>
-      <c r="N37" s="247"/>
-      <c r="O37" s="247"/>
-      <c r="P37" s="247"/>
-      <c r="Q37" s="247"/>
-      <c r="R37" s="247"/>
-      <c r="S37" s="247"/>
-      <c r="T37" s="247"/>
-      <c r="U37" s="247"/>
-      <c r="V37" s="247"/>
-      <c r="W37" s="247"/>
-      <c r="X37" s="247"/>
-      <c r="Y37" s="247"/>
-      <c r="Z37" s="247"/>
-      <c r="AA37" s="247"/>
+      <c r="B37" s="242"/>
+      <c r="C37" s="242"/>
+      <c r="D37" s="242"/>
+      <c r="E37" s="242"/>
+      <c r="F37" s="242"/>
+      <c r="G37" s="242"/>
+      <c r="H37" s="242"/>
+      <c r="I37" s="242"/>
+      <c r="J37" s="242"/>
+      <c r="K37" s="242"/>
+      <c r="L37" s="242"/>
+      <c r="M37" s="242"/>
+      <c r="N37" s="242"/>
+      <c r="O37" s="242"/>
+      <c r="P37" s="242"/>
+      <c r="Q37" s="242"/>
+      <c r="R37" s="242"/>
+      <c r="S37" s="242"/>
+      <c r="T37" s="242"/>
+      <c r="U37" s="242"/>
+      <c r="V37" s="242"/>
+      <c r="W37" s="242"/>
+      <c r="X37" s="242"/>
+      <c r="Y37" s="242"/>
+      <c r="Z37" s="242"/>
+      <c r="AA37" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -16613,18 +16543,18 @@
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A64" s="248" t="s">
+      <c r="A64" s="243" t="s">
         <v>256</v>
       </c>
-      <c r="B64" s="248"/>
-      <c r="C64" s="248"/>
-      <c r="D64" s="248"/>
-      <c r="E64" s="248"/>
-      <c r="F64" s="248"/>
-      <c r="G64" s="248"/>
-      <c r="H64" s="248"/>
-      <c r="I64" s="248"/>
-      <c r="J64" s="248"/>
+      <c r="B64" s="243"/>
+      <c r="C64" s="243"/>
+      <c r="D64" s="243"/>
+      <c r="E64" s="243"/>
+      <c r="F64" s="243"/>
+      <c r="G64" s="243"/>
+      <c r="H64" s="243"/>
+      <c r="I64" s="243"/>
+      <c r="J64" s="243"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="62" t="s">
@@ -18685,30 +18615,30 @@
       <c r="A47" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B47" s="244" t="s">
+      <c r="B47" s="239" t="s">
         <v>311</v>
       </c>
-      <c r="C47" s="244"/>
-      <c r="D47" s="244"/>
-      <c r="E47" s="244"/>
-      <c r="F47" s="244"/>
-      <c r="G47" s="244"/>
-      <c r="H47" s="244"/>
-      <c r="I47" s="244"/>
+      <c r="C47" s="239"/>
+      <c r="D47" s="239"/>
+      <c r="E47" s="239"/>
+      <c r="F47" s="239"/>
+      <c r="G47" s="239"/>
+      <c r="H47" s="239"/>
+      <c r="I47" s="239"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B49" s="244" t="s">
+      <c r="B49" s="239" t="s">
         <v>312</v>
       </c>
-      <c r="C49" s="244"/>
-      <c r="D49" s="244"/>
-      <c r="E49" s="244"/>
-      <c r="F49" s="244"/>
-      <c r="G49" s="244"/>
-      <c r="H49" s="244"/>
+      <c r="C49" s="239"/>
+      <c r="D49" s="239"/>
+      <c r="E49" s="239"/>
+      <c r="F49" s="239"/>
+      <c r="G49" s="239"/>
+      <c r="H49" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -20840,7 +20770,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="234">
-        <f>INDEX(Actuals!$B$2:$Z$2,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$2:$Y$2,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>150305.5</v>
       </c>
       <c r="C3" s="128">
@@ -20873,7 +20803,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="234">
-        <f>INDEX(Actuals!$B$3:$Z$3,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$3:$Y$3,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>3000</v>
       </c>
       <c r="C4" s="128">
@@ -20907,7 +20837,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="234">
-        <f>INDEX(Actuals!$B$4:$Z$4,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$4:$Y$4,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>380</v>
       </c>
       <c r="C5" s="128">
@@ -20955,7 +20885,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="234">
-        <f>INDEX(Actuals!$B$5:$Z$5,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$5:$Y$5,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>0</v>
       </c>
       <c r="C7" s="128">
@@ -20975,7 +20905,7 @@
         <v>F</v>
       </c>
       <c r="J7">
-        <f>INDEX(Actuals!$B$7:$Z$7,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$7:$Y$7,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>29000</v>
       </c>
     </row>
@@ -21204,7 +21134,7 @@
         <v>94</v>
       </c>
       <c r="B18" s="100">
-        <f>INDEX(Actuals!$B$7:$Z$7,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$7:$Y$7,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>29000</v>
       </c>
       <c r="C18" s="131">
@@ -21232,7 +21162,7 @@
         <v>95</v>
       </c>
       <c r="B19" s="100">
-        <f>INDEX(Actuals!$B$8:$Z$8,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$8:$Y$8,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>22000</v>
       </c>
       <c r="C19" s="131">
@@ -21260,7 +21190,7 @@
         <v>96</v>
       </c>
       <c r="B20" s="100">
-        <f>INDEX(Actuals!$B$9:$Z$9,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$9:$Y$9,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>22000</v>
       </c>
       <c r="C20" s="131">
@@ -21373,7 +21303,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="H28" s="249"/>
+      <c r="H28" s="238"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="160" t="s">
@@ -21395,7 +21325,7 @@
         <v>193</v>
       </c>
       <c r="B30" s="235">
-        <f>INDEX(Actuals!$B$15:$Z$15,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$15:$Y$15,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>42</v>
       </c>
       <c r="C30" s="123">
@@ -21411,11 +21341,11 @@
         <v>194</v>
       </c>
       <c r="B31" s="235">
-        <f>INDEX(Actuals!$B$16:$Z$16,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$16:$Y$16,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>54</v>
       </c>
       <c r="C31" s="167">
-        <f>B31-INDEX(Actuals!$B$16:$Z$16,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0))</f>
+        <f>B31-INDEX(Actuals!$B$16:$Y$16,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Y$1,0))</f>
         <v>1</v>
       </c>
       <c r="D31" s="123" t="s">
@@ -21434,7 +21364,7 @@
         <v>3659.1785714285716</v>
       </c>
       <c r="C32" s="131">
-        <f>IFERROR(B32-INDEX(Actuals!$B$6:$Z$6,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0))/INDEX(Actuals!$B$15:$Z$15,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0)),"—")</f>
+        <f>IFERROR(B32-INDEX(Actuals!$B$6:$Y$6,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Y$1,0))/INDEX(Actuals!$B$15:$Y$15,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Y$1,0)),"—")</f>
         <v>-6.8092334494772331</v>
       </c>
       <c r="D32" s="123" t="s">
@@ -21462,11 +21392,11 @@
         <v>620</v>
       </c>
       <c r="B34" s="28">
-        <f>INDEX(Retention!$B$6:$AZ$6,MATCH($I$2,Retention!$B$4:$AZ$4,0))</f>
+        <f>INDEX(Retention!$B$6:$AY$6,MATCH($I$2,Retention!$B$4:$AY$4,0))</f>
         <v>1</v>
       </c>
       <c r="C34" s="162">
-        <f>B34-INDEX(Retention!$B$6:$AZ$6,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Retention!$B$4:$AZ$4,0))</f>
+        <f>B34-INDEX(Retention!$B$6:$AY$6,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Retention!$B$4:$AY$4,0))</f>
         <v>3.8918026449843435E-3</v>
       </c>
       <c r="D34" s="123" t="s">
@@ -21478,11 +21408,11 @@
         <v>622</v>
       </c>
       <c r="B35" s="28">
-        <f>INDEX(Retention!$B$7:$AZ$7,MATCH($I$2,Retention!$B$4:$AZ$4,0))</f>
+        <f>INDEX(Retention!$B$7:$AY$7,MATCH($I$2,Retention!$B$4:$AY$4,0))</f>
         <v>1.00240271380201</v>
       </c>
       <c r="C35" s="162">
-        <f>B35-INDEX(Retention!$B$7:$AZ$7,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Retention!$B$4:$AZ$4,0))</f>
+        <f>B35-INDEX(Retention!$B$7:$AY$7,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Retention!$B$4:$AY$4,0))</f>
         <v>6.2945164469943027E-3</v>
       </c>
       <c r="D35" s="123" t="s">
@@ -21514,7 +21444,7 @@
         <v>29000</v>
       </c>
       <c r="C37" s="163">
-        <f>B37-INDEX(Actuals!$B$7:$Z$7,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0))</f>
+        <f>B37-INDEX(Actuals!$B$7:$Y$7,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Y$1,0))</f>
         <v>-2000</v>
       </c>
       <c r="D37" s="123" t="s">
@@ -21530,7 +21460,7 @@
         <v>14500</v>
       </c>
       <c r="C38" s="163">
-        <f>IFERROR(B38-INDEX(Actuals!$B$7:$Z$7,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0))/INDEX(Actuals!$B$14:$Z$14,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Z$1,0)),"—")</f>
+        <f>IFERROR(B38-INDEX(Actuals!$B$7:$Y$7,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Y$1,0))/INDEX(Actuals!$B$14:$Y$14,MATCH(DATE(YEAR($I$2),MONTH($I$2)-1,1),Actuals!$B$1:$Y$1,0)),"—")</f>
         <v>-1000</v>
       </c>
       <c r="D38" s="123" t="s">
@@ -21542,7 +21472,7 @@
         <v>664</v>
       </c>
       <c r="B39" s="235">
-        <f>INDEX(Actuals!$B$14:$Z$14,MATCH($I$2,Actuals!$B$1:$Z$1,0))</f>
+        <f>INDEX(Actuals!$B$14:$Y$14,MATCH($I$2,Actuals!$B$1:$Y$1,0))</f>
         <v>2</v>
       </c>
       <c r="C39" s="123" t="s">
@@ -21630,12 +21560,12 @@
         <v>636</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:5" ht="17" x14ac:dyDescent="0.4">
       <c r="A51" s="166" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="160" t="s">
         <v>4</v>
       </c>
@@ -21646,7 +21576,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="123" t="s">
         <v>616</v>
       </c>
@@ -21659,7 +21589,7 @@
         <v>3659.1785714285716</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="123" t="s">
         <v>620</v>
       </c>
@@ -21668,11 +21598,14 @@
         <v>1</v>
       </c>
       <c r="C55" s="162">
-        <f>Retention!AA6</f>
-        <v>0.99610819735501566</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+        <f>INDEX(Retention!$B$6:$AY$6, MATCH($I$2, Retention!$B$4:$AY$4,0))</f>
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="123" t="s">
         <v>622</v>
       </c>
@@ -21681,11 +21614,11 @@
         <v>1.00240271380201</v>
       </c>
       <c r="C56" s="162">
-        <f>Retention!AA7</f>
-        <v>0.99610819735501566</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+        <f>INDEX(Retention!$B$7:$AY$7, MATCH($I$2, Retention!$B$4:$AY$4,0))</f>
+        <v>1.00240271380201</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="123" t="s">
         <v>623</v>
       </c>
@@ -21698,7 +21631,7 @@
         <v>N/A — no losses</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="123" t="s">
         <v>640</v>
       </c>
@@ -21711,28 +21644,28 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="124" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="243" t="str">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="237" t="str">
         <f>TEXT($I$2,"mmmm yyyy")&amp;" — Closing MRR: "&amp;TEXT(B9,"$#,##0")&amp;" | NRR: "&amp;TEXT(B35,"0.0%")&amp;" | EBITDA margin: "&amp;TEXT(B23,"0.0%")</f>
         <v>March 2026 — Closing MRR: $153,686 | NRR: 100.2% | EBITDA margin: 22.5%</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="212" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="212" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="212" t="s">
         <v>733</v>
       </c>
@@ -23140,11 +23073,11 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="245" t="s">
+      <c r="A18" s="240" t="s">
         <v>644</v>
       </c>
-      <c r="B18" s="245"/>
-      <c r="C18" s="245"/>
+      <c r="B18" s="240"/>
+      <c r="C18" s="240"/>
       <c r="D18" s="122"/>
       <c r="E18" s="122"/>
     </row>

--- a/submissions/excel/excel_09_workbook_redesign.xlsx
+++ b/submissions/excel/excel_09_workbook_redesign.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\venti\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\venti\Downloads\idynamics-training\idynamics-analyst-training\submissions\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC441400-C005-4F93-994C-E2F6870EF094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2F5B96-754B-4620-8298-12F56FE82680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="billing_jan_2026" sheetId="16" r:id="rId1"/>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2889" uniqueCount="1074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2906" uniqueCount="1091">
   <si>
     <t>HISTORICAL BASELINE — 2024 &amp; 2025 ACTUALS</t>
   </si>
@@ -4560,6 +4560,57 @@
   </si>
   <si>
     <t>Feb-26</t>
+  </si>
+  <si>
+    <t>Part 5:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The billing file represents a point in time record while the database represents a historical period. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">They share the same number therefore $2185 is the correct number. </t>
+  </si>
+  <si>
+    <t>The billing file for January shows $2185 for SUB012.</t>
+  </si>
+  <si>
+    <t>The database for January shows $2185 for SUB012.</t>
+  </si>
+  <si>
+    <t>Part 6:</t>
+  </si>
+  <si>
+    <t>The negative row is row number 36.</t>
+  </si>
+  <si>
+    <t>This row relates to Ontario Manufacturing Tech and their monthly Analytics Starter subscription.</t>
+  </si>
+  <si>
+    <t>A refund was issued because OMT cancelled their subscription on 2026-02-20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since a refund was issued, total collected will be lowered. They were billed at the beginning of the month and because of the cancellation occurring near the end, they received a prorated refund. </t>
+  </si>
+  <si>
+    <t>Total billed will also be reduced since the billing system recorded that the invoice was partially reversed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commentary: </t>
+  </si>
+  <si>
+    <t>Not all of the January revenue was collected within the month. This is because of Prairie SaaS Innovations (SUB028) which failed a $675 payment on January 20th due to insufficient funds. This was resolved on February 5th.</t>
+  </si>
+  <si>
+    <t>As of January 31st, 2026, the deferred revenue was high due to the previously mentioned annual subscriptions. This is very critical to monitor as it reflects our future obligations to deliver services which have already been paid for.</t>
+  </si>
+  <si>
+    <t>For data integrity, the reconcilliation check confirms that the billing file and database match for certain records like SUB012 ($2185) but it should be recognized by analysts that the billing file is a point in time snapshot while the database has historical records.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Along with this, the negative entry from Ontario Manufacturing Tech (SUB050) comes from a prorated refund on February 20th following a cancellation in the middle of the month. This confirms that when the billing system properly records partial reversals, downstream reporting should be audited to make sure these changes are reflected. </t>
+  </si>
+  <si>
+    <t>The difference between MRR and cash collected is driven by payment timing. Specifically, the prepayments from Pacific Analytics for SUB002 ($46,800) and SUB054 ($23,826) inflated the total invoiced amount above MRR.</t>
   </si>
 </sst>
 </file>
@@ -5970,6 +6021,54 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -6077,54 +6176,6 @@
     <dxf>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -6144,14 +6195,14 @@
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{08D930B4-9890-411B-810C-899FE4673D42}" name="invoice_id"/>
     <tableColumn id="2" xr3:uid="{78C5F7D2-C96A-41A2-90A4-0E4C08695DF6}" name="invoice_number"/>
-    <tableColumn id="3" xr3:uid="{80B802A6-F76B-4BE6-A795-8C34D532C099}" name="invoice_date" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{80B802A6-F76B-4BE6-A795-8C34D532C099}" name="invoice_date" dataDxfId="45"/>
     <tableColumn id="4" xr3:uid="{203A3EE7-952D-4AFE-8BAC-C41BD7CA8655}" name="customer_id"/>
     <tableColumn id="5" xr3:uid="{EC0856AA-B208-44D8-97CD-3DD96CABD659}" name="customer_name"/>
     <tableColumn id="6" xr3:uid="{E391B6F2-AE8C-492A-AED4-AB5909088DDF}" name="subscription_id"/>
     <tableColumn id="7" xr3:uid="{074C8C73-3126-45BE-9B27-A5BC005C1EFF}" name="plan_name"/>
     <tableColumn id="8" xr3:uid="{F0D5F54C-B34A-4267-B3FD-4C83D8A50209}" name="billing_cycle"/>
-    <tableColumn id="9" xr3:uid="{6E760CB8-3FA8-436E-A4CD-72E1C0B10013}" name="period_start" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{B787FCB1-15F0-460E-A722-14899CAC199A}" name="period_end" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{6E760CB8-3FA8-436E-A4CD-72E1C0B10013}" name="period_start" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{B787FCB1-15F0-460E-A722-14899CAC199A}" name="period_end" dataDxfId="43"/>
     <tableColumn id="11" xr3:uid="{81564DDC-B43B-4569-99BA-B0601A2EEE03}" name="seats"/>
     <tableColumn id="12" xr3:uid="{B615AF31-2E34-4DE2-BE04-C72D72BE94AF}" name="unit_price_usd"/>
     <tableColumn id="13" xr3:uid="{A983E25A-17DC-42D0-9713-BE9B5E00A732}" name="subtotal"/>
@@ -6159,7 +6210,7 @@
     <tableColumn id="15" xr3:uid="{A079E266-8647-4132-BF2B-629C26246AAD}" name="discount_amount"/>
     <tableColumn id="16" xr3:uid="{FD389F69-CE39-4BF7-B6A4-43A116F762AD}" name="amount_due_usd"/>
     <tableColumn id="17" xr3:uid="{D735EA05-5C6F-4FDC-90B2-EA5C2DF9FD52}" name="status"/>
-    <tableColumn id="18" xr3:uid="{A31C9E02-6CED-4D0F-BCBF-92D564CE7AAA}" name="payment_date" dataDxfId="40"/>
+    <tableColumn id="18" xr3:uid="{A31C9E02-6CED-4D0F-BCBF-92D564CE7AAA}" name="payment_date" dataDxfId="42"/>
     <tableColumn id="19" xr3:uid="{57ECA177-DABC-4800-BB5B-13C0DC93FCD7}" name="failure_reason"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6236,14 +6287,14 @@
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{21B141D2-BD24-4523-B0A8-8B99DCD9FECF}" name="invoice_id"/>
     <tableColumn id="2" xr3:uid="{AB269321-8EAB-4325-AE18-6279930F9A0E}" name="invoice_number"/>
-    <tableColumn id="3" xr3:uid="{23106853-3100-4D36-9C47-4269F0C551BD}" name="invoice_date" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{23106853-3100-4D36-9C47-4269F0C551BD}" name="invoice_date" dataDxfId="49"/>
     <tableColumn id="4" xr3:uid="{EE76C4DA-5FA6-436E-9A78-AFEC5CFC83C1}" name="customer_id"/>
     <tableColumn id="5" xr3:uid="{2760AFFA-3B13-4B9F-99D3-C9E01F37B22F}" name="customer_name"/>
     <tableColumn id="6" xr3:uid="{4CE635A9-DE25-4E9B-BB83-9C94555717D5}" name="subscription_id"/>
     <tableColumn id="7" xr3:uid="{E4C2A96F-D0B4-4656-BEE4-47DBECF891E0}" name="plan_name"/>
     <tableColumn id="8" xr3:uid="{3A66C07F-0245-4D4D-8D5A-953CAEAD58D3}" name="billing_cycle"/>
-    <tableColumn id="9" xr3:uid="{942367B1-6210-4321-9324-F81D1DD3398A}" name="period_start" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{D0AF7F7C-63C8-4F36-954F-161F43408DA8}" name="period_end" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{942367B1-6210-4321-9324-F81D1DD3398A}" name="period_start" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{D0AF7F7C-63C8-4F36-954F-161F43408DA8}" name="period_end" dataDxfId="47"/>
     <tableColumn id="11" xr3:uid="{4EA378D3-B2C9-4C09-BE53-469ED430F32B}" name="seats"/>
     <tableColumn id="12" xr3:uid="{146801D2-0FD0-4981-87DE-8E2A43F60772}" name="unit_price_usd"/>
     <tableColumn id="13" xr3:uid="{FF4311AE-A6A1-4E7B-9FC9-11B3B4A8414C}" name="subtotal"/>
@@ -6251,7 +6302,7 @@
     <tableColumn id="15" xr3:uid="{C6C9646C-0AEB-4ED2-9FBD-F0441AC39D6A}" name="discount_amount"/>
     <tableColumn id="16" xr3:uid="{732082CD-B258-40E8-A9EA-7C2D2512099B}" name="amount_due_usd"/>
     <tableColumn id="17" xr3:uid="{FE7CEB2C-A5AF-4EFF-BF96-1D794C072BDF}" name="status"/>
-    <tableColumn id="18" xr3:uid="{0FFB9F63-EAE9-445D-B021-79D4C9AA1AE4}" name="payment_date" dataDxfId="36"/>
+    <tableColumn id="18" xr3:uid="{0FFB9F63-EAE9-445D-B021-79D4C9AA1AE4}" name="payment_date" dataDxfId="46"/>
     <tableColumn id="19" xr3:uid="{168E90D3-C284-41BD-91C7-13D5D2A06E50}" name="failure_reason"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6262,13 +6313,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{77B4CBBC-3B91-4F77-832A-360696F58DDA}" name="Table8" displayName="Table8" ref="A5:G51" totalsRowShown="0">
   <autoFilter ref="A5:G51" xr:uid="{77B4CBBC-3B91-4F77-832A-360696F58DDA}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{6D854B12-0D02-49F8-A839-BC3EC59A51C8}" name="transaction_date" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{26B51931-C320-4C09-BAE3-DB23FE00802A}" name="post_date" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{6D854B12-0D02-49F8-A839-BC3EC59A51C8}" name="transaction_date" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{26B51931-C320-4C09-BAE3-DB23FE00802A}" name="post_date" dataDxfId="40"/>
     <tableColumn id="3" xr3:uid="{28B78116-4AC0-4D06-A5B8-EC593DDCDA0A}" name="description"/>
     <tableColumn id="4" xr3:uid="{9B35B6BB-60A0-43F8-AF13-5F5533C469AF}" name="type"/>
-    <tableColumn id="5" xr3:uid="{13102D05-6A87-4E3A-87E4-4B2ED885C316}" name="amount" dataDxfId="33" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{13102D05-6A87-4E3A-87E4-4B2ED885C316}" name="amount" dataDxfId="39" dataCellStyle="Currency"/>
     <tableColumn id="6" xr3:uid="{F78163CC-E0F5-4793-840D-6BE5D7B69995}" name="reference_number"/>
-    <tableColumn id="7" xr3:uid="{C0F020B1-F1A8-44DE-B2DD-CC8BC9859A33}" name="running_balance" dataDxfId="32" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{C0F020B1-F1A8-44DE-B2DD-CC8BC9859A33}" name="running_balance" dataDxfId="38" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6278,13 +6329,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{996F6FD3-8166-4C9D-868A-DCA1BDDC71ED}" name="Table9" displayName="Table9" ref="A5:G54" totalsRowShown="0">
   <autoFilter ref="A5:G54" xr:uid="{996F6FD3-8166-4C9D-868A-DCA1BDDC71ED}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9D45E691-BD42-4DDE-8170-A19F3EB822D9}" name="transaction_date" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{EE01DCDB-A1DC-47FA-930F-7B8C4DDE45BE}" name="post_date" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{9D45E691-BD42-4DDE-8170-A19F3EB822D9}" name="transaction_date" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{EE01DCDB-A1DC-47FA-930F-7B8C4DDE45BE}" name="post_date" dataDxfId="36"/>
     <tableColumn id="3" xr3:uid="{E524376A-0CE3-4A5B-AD61-DF9ECF465A47}" name="description"/>
     <tableColumn id="4" xr3:uid="{818AAD8E-991B-430D-B740-8956E60587D6}" name="type"/>
-    <tableColumn id="5" xr3:uid="{BED9FE2E-6D3F-44BB-964E-B04E7428A7E1}" name="amount" dataDxfId="29" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{BED9FE2E-6D3F-44BB-964E-B04E7428A7E1}" name="amount" dataDxfId="35" dataCellStyle="Currency"/>
     <tableColumn id="6" xr3:uid="{DCC1B946-4880-41A9-B7B0-DAC27E51E4A9}" name="reference_number"/>
-    <tableColumn id="7" xr3:uid="{3381FA1C-207B-402F-90C9-51AA6B8ECF02}" name="running_balance" dataDxfId="28" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{3381FA1C-207B-402F-90C9-51AA6B8ECF02}" name="running_balance" dataDxfId="34" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6295,8 +6346,8 @@
   <autoFilter ref="A1:C6" xr:uid="{9534377B-632C-4D93-93C6-A4166D213A4F}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{71EA2AFF-48ED-4A6D-AF45-62B20DAE65F2}" name="Metric"/>
-    <tableColumn id="2" xr3:uid="{F597A9C7-D774-4FA8-8ADE-1B56C0322542}" name="Jan-26" dataDxfId="49" dataCellStyle="Currency"/>
-    <tableColumn id="3" xr3:uid="{A6B9495D-88AD-4589-BF55-33BCF9462EDF}" name="Feb-26" dataDxfId="48" dataCellStyle="Currency"/>
+    <tableColumn id="2" xr3:uid="{F597A9C7-D774-4FA8-8ADE-1B56C0322542}" name="Jan-26" dataDxfId="33" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{A6B9495D-88AD-4589-BF55-33BCF9462EDF}" name="Feb-26" dataDxfId="32" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6307,8 +6358,8 @@
   <autoFilter ref="A9:C14" xr:uid="{34B0B22A-E5A8-466B-9B11-EA054D4912F5}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{16B9F025-8A2C-4F04-8AFD-F2ED46843CB0}" name="Item"/>
-    <tableColumn id="2" xr3:uid="{D7FCAE38-41A2-4A5B-92A3-AFFCD9A06438}" name="Jan-26" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{835A3DF2-EEDA-44C2-BD07-E82A2D5568A5}" name="Feb-26" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{D7FCAE38-41A2-4A5B-92A3-AFFCD9A06438}" name="Jan-26" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{835A3DF2-EEDA-44C2-BD07-E82A2D5568A5}" name="Feb-26" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6319,8 +6370,8 @@
   <autoFilter ref="A17:C20" xr:uid="{118881AB-F941-440B-84B6-3694135FB9B3}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{736FAE13-AEF8-4957-98B5-9EA96B231F97}" name="Item"/>
-    <tableColumn id="2" xr3:uid="{9488147C-4BC7-49A2-B78B-AB43AAE241A5}" name="Jan-26" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{CE43E3F8-3FEA-46B8-AEF7-ADDCDFB72AE7}" name="Feb-26" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{9488147C-4BC7-49A2-B78B-AB43AAE241A5}" name="Jan-26" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{CE43E3F8-3FEA-46B8-AEF7-ADDCDFB72AE7}" name="Feb-26" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -30259,7 +30310,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4300007B-0F7A-471B-BF41-033345593E90}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.26953125" bestFit="1" customWidth="1"/>
@@ -30295,12 +30346,12 @@
         <v>1061</v>
       </c>
       <c r="B3" s="39">
-        <f>SUM(billing_jan_2026!P2:P30)+SUM(billing_jan_2026!P32:P48)</f>
-        <v>177975</v>
+        <f>SUM(billing_jan_2026!P2:P48)</f>
+        <v>178650</v>
       </c>
       <c r="C3" s="39">
-        <f>SUM(billing_feb_2026!P2:P35) + SUM(billing_feb_2026!P37:P49)</f>
-        <v>114144</v>
+        <f>SUM(billing_feb_2026!P2:P49)</f>
+        <v>113974.29</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -30312,8 +30363,8 @@
         <v>177975</v>
       </c>
       <c r="C4" s="39">
-        <f>SUM(bank_statement_feb_2026!E6:E40)+SUM(bank_statement_feb_2026!E42:E54)</f>
-        <v>114819</v>
+        <f>SUM(bank_statement_feb_2026!E6:E54)</f>
+        <v>114649.29</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -30322,11 +30373,11 @@
       </c>
       <c r="B5" s="38">
         <f>B3-B2</f>
-        <v>33195.5</v>
+        <v>33870.5</v>
       </c>
       <c r="C5" s="38">
         <f>C3-C2</f>
-        <v>-36161.5</v>
+        <v>-36331.210000000006</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -30335,7 +30386,7 @@
       </c>
       <c r="B6" s="38">
         <f>B3-B4</f>
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="C6" s="38">
         <f>C3-C4</f>
@@ -30376,12 +30427,12 @@
         <v>1066</v>
       </c>
       <c r="B11" s="38">
-        <f>B4-B2</f>
-        <v>33195.5</v>
+        <f xml:space="preserve"> SUMIF(billing_jan_2026!H:H, "Annual", billing_jan_2026!P:P) * (11/12)</f>
+        <v>64740.5</v>
       </c>
       <c r="C11" s="38">
-        <f>C4-C2</f>
-        <v>-35486.5</v>
+        <f xml:space="preserve"> SUMIF(billing_feb_2026!H:H, "Annual", billing_feb_2026!P:P) * (11/12)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -30389,11 +30440,12 @@
         <v>1067</v>
       </c>
       <c r="B12" s="38">
-        <v>0</v>
+        <f xml:space="preserve"> (billing_jan_2026!P34 + billing_jan_2026!P37) / 12</f>
+        <v>5885.5</v>
       </c>
       <c r="C12" s="38">
-        <f>((billing_jan_2026!M34+billing_jan_2026!M37)/12)*2</f>
-        <v>11980</v>
+        <f xml:space="preserve"> (billing_jan_2026!P34 + billing_jan_2026!P37) / 12</f>
+        <v>5885.5</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -30402,11 +30454,11 @@
       </c>
       <c r="B13" s="38">
         <f>B10+B11</f>
-        <v>177975</v>
+        <v>209520</v>
       </c>
       <c r="C13" s="38">
         <f>C10+C11-C12</f>
-        <v>102839</v>
+        <v>144420</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -30415,11 +30467,11 @@
       </c>
       <c r="B14" s="38">
         <f>B13-B3</f>
-        <v>0</v>
+        <v>30870</v>
       </c>
       <c r="C14" s="38">
         <f>C13-C3</f>
-        <v>-11305</v>
+        <v>30445.710000000006</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -30444,11 +30496,11 @@
       </c>
       <c r="B18" s="38">
         <f>B3</f>
-        <v>177975</v>
+        <v>178650</v>
       </c>
       <c r="C18" s="38">
         <f>C3</f>
-        <v>114144</v>
+        <v>113974.29</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -30456,12 +30508,12 @@
         <v>1062</v>
       </c>
       <c r="B19" s="38">
-        <f>B18</f>
+        <f>B4</f>
         <v>177975</v>
       </c>
       <c r="C19" s="38">
         <f>C4</f>
-        <v>114819</v>
+        <v>114649.29</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -30470,13 +30522,98 @@
       </c>
       <c r="B20" s="38">
         <f>B19-B18</f>
-        <v>0</v>
+        <v>-675</v>
       </c>
       <c r="C20" s="38">
         <f>C19-C18</f>
         <v>675</v>
       </c>
       <c r="F20" s="38"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="42" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="42" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="42" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>1089</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
